--- a/7_Alola_Data.xlsx
+++ b/7_Alola_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G229"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,10 +430,10 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C2" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>Pikipek</v>
@@ -453,10 +453,10 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C3" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>Yungoos</v>
@@ -476,10 +476,10 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C4" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>Rattata</v>
@@ -499,10 +499,10 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C5" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>Ledyba</v>
@@ -522,10 +522,10 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C6" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>Spinarak</v>
@@ -545,10 +545,10 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C7" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v>Grubbin</v>
@@ -568,10 +568,10 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C8" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>Pichu</v>
@@ -591,10 +591,10 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>Route 1</v>
+        <v>Route 1 East</v>
       </c>
       <c r="C9" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v>Pikachu</v>
@@ -614,10 +614,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B10" t="str">
-        <v>Route 1</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C10" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>Inkay</v>
@@ -637,10 +637,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B11" t="str">
-        <v>Route 1</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C11" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>Slowpoke</v>
@@ -660,10 +660,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B12" t="str">
-        <v>Route 1</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C12" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v/>
       </c>
       <c r="D12" t="str">
         <v>Meowth</v>
@@ -683,10 +683,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B13" t="str">
-        <v>Route 1</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C13" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v>Tentacool</v>
@@ -706,10 +706,10 @@
         <v>Challenge 1</v>
       </c>
       <c r="B14" t="str">
-        <v>Route 1</v>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="C14" t="str">
-        <v>Hau'oli Outskirts</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>Finneon</v>
@@ -729,10 +729,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B15" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C15" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D15" t="str">
         <v>Drowzee</v>
@@ -752,10 +752,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B16" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C16" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D16" t="str">
         <v>Makuhita</v>
@@ -775,10 +775,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B17" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C17" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D17" t="str">
         <v>Spearow</v>
@@ -798,10 +798,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B18" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C18" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v>Ekans</v>
@@ -821,10 +821,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B19" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C19" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D19" t="str">
         <v>Growlithe</v>
@@ -844,10 +844,10 @@
         <v>Challenge 2</v>
       </c>
       <c r="B20" t="str">
-        <v>Route 2</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C20" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D20" t="str">
         <v>Smeargle</v>
@@ -864,22 +864,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B21" t="str">
-        <v>Captain Ilima</v>
+        <v>Route 2 North</v>
       </c>
       <c r="C21" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>Crabrawler</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>7-12</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>10.00%</v>
       </c>
       <c r="G21" t="str">
         <v>0</v>
@@ -887,22 +887,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Challenge 4</v>
+        <v/>
       </c>
       <c r="B22" t="str">
-        <v>Hau'oli Cemetery</v>
+        <v>Captain Ilima Boss Battle</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>Gastly</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>10-15</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G22" t="str">
         <v>0</v>
@@ -919,7 +919,7 @@
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>Drifloon</v>
+        <v>Gastly</v>
       </c>
       <c r="E23" t="str">
         <v>10-15</v>
@@ -942,7 +942,7 @@
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>Murkrow</v>
+        <v>Drifloon</v>
       </c>
       <c r="E24" t="str">
         <v>10-15</v>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>Misdreavus</v>
+        <v>Murkrow</v>
       </c>
       <c r="E25" t="str">
         <v>10-15</v>
@@ -979,22 +979,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Challenge 5</v>
+        <v>Challenge 4</v>
       </c>
       <c r="B26" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Hau'oli Cemetery</v>
       </c>
       <c r="C26" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D26" t="str">
-        <v>Roggenrola</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E26" t="str">
-        <v>14-19</v>
+        <v>10-15</v>
       </c>
       <c r="F26" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G26" t="str">
         <v>0</v>
@@ -1005,13 +1005,13 @@
         <v>Challenge 5</v>
       </c>
       <c r="B27" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C27" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D27" t="str">
-        <v>Carbink</v>
+        <v>Roggenrola</v>
       </c>
       <c r="E27" t="str">
         <v>14-19</v>
@@ -1028,13 +1028,13 @@
         <v>Challenge 5</v>
       </c>
       <c r="B28" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C28" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D28" t="str">
-        <v>Spinda</v>
+        <v>Carbink</v>
       </c>
       <c r="E28" t="str">
         <v>14-19</v>
@@ -1051,13 +1051,13 @@
         <v>Challenge 5</v>
       </c>
       <c r="B29" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C29" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D29" t="str">
-        <v>Mawile</v>
+        <v>Spinda</v>
       </c>
       <c r="E29" t="str">
         <v>14-19</v>
@@ -1074,13 +1074,13 @@
         <v>Challenge 5</v>
       </c>
       <c r="B30" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C30" t="str">
-        <v>Farthest Hollow</v>
+        <v/>
       </c>
       <c r="D30" t="str">
-        <v>Lycanroc</v>
+        <v>Mawile</v>
       </c>
       <c r="E30" t="str">
         <v>14-19</v>
@@ -1094,22 +1094,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Challenge 6</v>
+        <v>Challenge 5</v>
       </c>
       <c r="B31" t="str">
-        <v>Seaward Cave</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>Barboach</v>
+        <v>Lycanroc</v>
       </c>
       <c r="E31" t="str">
-        <v>16-21</v>
+        <v>14-19</v>
       </c>
       <c r="F31" t="str">
-        <v>33.33%</v>
+        <v>20.00%</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
@@ -1117,22 +1117,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Challenge 6</v>
+        <v>Challenge 5</v>
       </c>
       <c r="B32" t="str">
-        <v>Seaward Cave</v>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>Smoochum</v>
+        <v>Rockruff</v>
       </c>
       <c r="E32" t="str">
-        <v>16-21</v>
+        <v>14-19</v>
       </c>
       <c r="F32" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
       <c r="G32" t="str">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>Seel</v>
+        <v>Barboach</v>
       </c>
       <c r="E33" t="str">
         <v>16-21</v>
@@ -1163,22 +1163,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B34" t="str">
-        <v>Kahuna Hala</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C34" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>Smoochum</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>16-21</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>33.33%</v>
       </c>
       <c r="G34" t="str">
         <v>0</v>
@@ -1186,22 +1186,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Challenge 8</v>
+        <v>Challenge 6</v>
       </c>
       <c r="B35" t="str">
-        <v>Paniola Ranch</v>
+        <v>Seaward Cave</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>Eevee</v>
+        <v>Seel</v>
       </c>
       <c r="E35" t="str">
-        <v>20-25</v>
+        <v>16-21</v>
       </c>
       <c r="F35" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G35" t="str">
         <v>0</v>
@@ -1209,22 +1209,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Challenge 8</v>
+        <v/>
       </c>
       <c r="B36" t="str">
-        <v>Paniola Ranch</v>
+        <v>Kahuna Hala Boss Battle</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>Mareep</v>
+        <v/>
       </c>
       <c r="E36" t="str">
-        <v>20-25</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G36" t="str">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>Tauros</v>
+        <v>Eevee</v>
       </c>
       <c r="E37" t="str">
         <v>20-25</v>
@@ -1264,7 +1264,7 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>Miltank</v>
+        <v>Mareep</v>
       </c>
       <c r="E38" t="str">
         <v>20-25</v>
@@ -1278,22 +1278,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Challenge 9</v>
+        <v>Challenge 8</v>
       </c>
       <c r="B39" t="str">
-        <v>Daycare</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C39" t="str">
-        <v>NPC</v>
+        <v/>
       </c>
       <c r="D39" t="str">
-        <v/>
+        <v>Tauros</v>
       </c>
       <c r="E39" t="str">
-        <v/>
+        <v>20-25</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G39" t="str">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 8</v>
       </c>
       <c r="B40" t="str">
-        <v>Route 5</v>
+        <v>Paniola Ranch</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>Noibat</v>
+        <v>Miltank</v>
       </c>
       <c r="E40" t="str">
-        <v>23-28</v>
+        <v>20-25</v>
       </c>
       <c r="F40" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
       <c r="G40" t="str">
         <v>0</v>
@@ -1324,22 +1324,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 9</v>
       </c>
       <c r="B41" t="str">
-        <v>Route 5</v>
+        <v>Daycare NPC</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>Fomantis</v>
+        <v/>
       </c>
       <c r="E41" t="str">
-        <v>23-28</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
       <c r="G41" t="str">
         <v>0</v>
@@ -1356,7 +1356,7 @@
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>Bounsweet</v>
+        <v>Noibat</v>
       </c>
       <c r="E42" t="str">
         <v>23-28</v>
@@ -1370,22 +1370,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v>Captain Lana</v>
+        <v>Route 5</v>
       </c>
       <c r="C43" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>Fomantis</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>23-28</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>33.33%</v>
       </c>
       <c r="G43" t="str">
         <v>0</v>
@@ -1393,19 +1393,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 5</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>Cubone</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E44" t="str">
-        <v>28-33</v>
+        <v>23-28</v>
       </c>
       <c r="F44" t="str">
         <v>33.33%</v>
@@ -1416,22 +1416,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B45" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Route 5</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>Kangaskhan</v>
+        <v>Dewpider</v>
       </c>
       <c r="E45" t="str">
-        <v>28-33</v>
+        <v>23-28</v>
       </c>
       <c r="F45" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
       <c r="G45" t="str">
         <v>0</v>
@@ -1439,22 +1439,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Challenge 12</v>
+        <v/>
       </c>
       <c r="B46" t="str">
-        <v>Wela Volcano Park</v>
+        <v>Captain Lana Boss Battle</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>Magby</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>28-33</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
       <c r="G46" t="str">
         <v>0</v>
@@ -1462,22 +1462,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B47" t="str">
-        <v>Captain Kiawe</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C47" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>Cubone</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>28-33</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>33.33%</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B48" t="str">
-        <v>Route 7</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>Staryu</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E48" t="str">
-        <v>31-36</v>
+        <v>28-33</v>
       </c>
       <c r="F48" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G48" t="str">
         <v>0</v>
@@ -1508,22 +1508,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B49" t="str">
-        <v>Route 7</v>
+        <v>Wela Volcano Park</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>Pyukumuku</v>
+        <v>Magby</v>
       </c>
       <c r="E49" t="str">
-        <v>31-36</v>
+        <v>28-33</v>
       </c>
       <c r="F49" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G49" t="str">
         <v>0</v>
@@ -1531,22 +1531,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Challenge 14</v>
+        <v/>
       </c>
       <c r="B50" t="str">
-        <v>Route 7</v>
+        <v>Captain Kiawe Boss Battle</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>Corsola</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>31-36</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>20.00%</v>
+        <v/>
       </c>
       <c r="G50" t="str">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>Mareanie</v>
+        <v>Staryu</v>
       </c>
       <c r="E51" t="str">
         <v>31-36</v>
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>Bruxish</v>
+        <v>Pyukumuku</v>
       </c>
       <c r="E52" t="str">
         <v>31-36</v>
@@ -1600,19 +1600,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B53" t="str">
-        <v>Route 8</v>
+        <v>Route 7</v>
       </c>
       <c r="C53" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D53" t="str">
-        <v>Omanyte</v>
+        <v>Corsola</v>
       </c>
       <c r="E53" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F53" t="str">
         <v>20.00%</v>
@@ -1623,19 +1623,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B54" t="str">
-        <v>Route 8</v>
+        <v>Route 7</v>
       </c>
       <c r="C54" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D54" t="str">
-        <v>Kabuto</v>
+        <v>Mareanie</v>
       </c>
       <c r="E54" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F54" t="str">
         <v>20.00%</v>
@@ -1646,19 +1646,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B55" t="str">
-        <v>Route 8</v>
+        <v>Route 7</v>
       </c>
       <c r="C55" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D55" t="str">
-        <v>Lileep</v>
+        <v>Bruxish</v>
       </c>
       <c r="E55" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F55" t="str">
         <v>20.00%</v>
@@ -1669,22 +1669,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B56" t="str">
-        <v>Route 8</v>
+        <v>Route 7</v>
       </c>
       <c r="C56" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D56" t="str">
-        <v>Anorith</v>
+        <v>Wishiwashi</v>
       </c>
       <c r="E56" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F56" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G56" t="str">
         <v>0</v>
@@ -1695,13 +1695,13 @@
         <v>Challenge 15</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C57" t="str">
-        <v>Fossil Restoration Center Part 1</v>
+        <v/>
       </c>
       <c r="D57" t="str">
-        <v>Cranidos</v>
+        <v>Omanyte</v>
       </c>
       <c r="E57" t="str">
         <v>32-37</v>
@@ -1715,16 +1715,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B58" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C58" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D58" t="str">
-        <v>Shieldon</v>
+        <v>Kabuto</v>
       </c>
       <c r="E58" t="str">
         <v>32-37</v>
@@ -1738,16 +1738,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B59" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C59" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D59" t="str">
-        <v>Archen</v>
+        <v>Lileep</v>
       </c>
       <c r="E59" t="str">
         <v>32-37</v>
@@ -1761,16 +1761,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B60" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C60" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D60" t="str">
-        <v>Tirtouga</v>
+        <v>Anorith</v>
       </c>
       <c r="E60" t="str">
         <v>32-37</v>
@@ -1784,16 +1784,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B61" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="C61" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D61" t="str">
-        <v>Tyrunt</v>
+        <v>Cranidos</v>
       </c>
       <c r="E61" t="str">
         <v>32-37</v>
@@ -1810,13 +1810,13 @@
         <v/>
       </c>
       <c r="B62" t="str">
-        <v>Route 8</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C62" t="str">
-        <v>Fossil Restoration Center Part 2</v>
+        <v/>
       </c>
       <c r="D62" t="str">
-        <v>Amaura</v>
+        <v>Shieldon</v>
       </c>
       <c r="E62" t="str">
         <v>32-37</v>
@@ -1830,22 +1830,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Challenge 16</v>
+        <v/>
       </c>
       <c r="B63" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C63" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D63" t="str">
-        <v>Trumbeak</v>
+        <v>Archen</v>
       </c>
       <c r="E63" t="str">
-        <v>34-39</v>
+        <v>32-37</v>
       </c>
       <c r="F63" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G63" t="str">
         <v>0</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Challenge 16</v>
+        <v/>
       </c>
       <c r="B64" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C64" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D64" t="str">
-        <v>Steenee</v>
+        <v>Tirtouga</v>
       </c>
       <c r="E64" t="str">
-        <v>34-39</v>
+        <v>32-37</v>
       </c>
       <c r="F64" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G64" t="str">
         <v>0</v>
@@ -1876,22 +1876,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Challenge 16</v>
+        <v/>
       </c>
       <c r="B65" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C65" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D65" t="str">
-        <v>Comfey</v>
+        <v>Tyrunt</v>
       </c>
       <c r="E65" t="str">
-        <v>34-39</v>
+        <v>32-37</v>
       </c>
       <c r="F65" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G65" t="str">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Challenge 16</v>
+        <v/>
       </c>
       <c r="B66" t="str">
-        <v>Lush Jungle</v>
+        <v>Route 8 Fossil Restoration Center Part 2</v>
       </c>
       <c r="C66" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D66" t="str">
-        <v>Hoothoot</v>
+        <v>Amaura</v>
       </c>
       <c r="E66" t="str">
-        <v>34-39</v>
+        <v>32-37</v>
       </c>
       <c r="F66" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G66" t="str">
         <v>0</v>
@@ -1925,13 +1925,13 @@
         <v>Challenge 16</v>
       </c>
       <c r="B67" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C67" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D67" t="str">
-        <v>Oranguru</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E67" t="str">
         <v>34-39</v>
@@ -1948,13 +1948,13 @@
         <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C68" t="str">
-        <v>North</v>
+        <v/>
       </c>
       <c r="D68" t="str">
-        <v>Bounsweet</v>
+        <v>Steenee</v>
       </c>
       <c r="E68" t="str">
         <v>34-39</v>
@@ -1968,22 +1968,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C69" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D69" t="str">
-        <v>Golbat</v>
+        <v>Comfey</v>
       </c>
       <c r="E69" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F69" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G69" t="str">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B70" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C70" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D70" t="str">
-        <v>Salandit</v>
+        <v>Hoothoot</v>
       </c>
       <c r="E70" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F70" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G70" t="str">
         <v>0</v>
@@ -2014,22 +2014,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B71" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C71" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D71" t="str">
-        <v>Larvesta</v>
+        <v>Oranguru</v>
       </c>
       <c r="E71" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F71" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G71" t="str">
         <v>0</v>
@@ -2037,22 +2037,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B72" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C72" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D72" t="str">
-        <v>Oranguru</v>
+        <v>Bounsweet</v>
       </c>
       <c r="E72" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F72" t="str">
-        <v>20.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G72" t="str">
         <v>0</v>
@@ -2060,22 +2060,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B73" t="str">
-        <v>Lush Jungle</v>
+        <v>Lush Jungle North</v>
       </c>
       <c r="C73" t="str">
-        <v>East Cave</v>
+        <v/>
       </c>
       <c r="D73" t="str">
-        <v>Passimian</v>
+        <v>Morelull</v>
       </c>
       <c r="E73" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F73" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G73" t="str">
         <v>0</v>
@@ -2083,22 +2083,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B74" t="str">
-        <v>Captain Mallow</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="C74" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>Golbat</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>35-40</v>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>20.00%</v>
       </c>
       <c r="G74" t="str">
         <v>0</v>
@@ -2106,22 +2106,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B75" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>Zubat</v>
+        <v>Salandit</v>
       </c>
       <c r="E75" t="str">
-        <v>38-43</v>
+        <v>35-40</v>
       </c>
       <c r="F75" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G75" t="str">
         <v>0</v>
@@ -2129,22 +2129,22 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B76" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>Diglett</v>
+        <v>Larvesta</v>
       </c>
       <c r="E76" t="str">
-        <v>38-43</v>
+        <v>35-40</v>
       </c>
       <c r="F76" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G76" t="str">
         <v>0</v>
@@ -2152,22 +2152,22 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B77" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>Kecleon</v>
+        <v>Oranguru</v>
       </c>
       <c r="E77" t="str">
-        <v>38-43</v>
+        <v>35-40</v>
       </c>
       <c r="F77" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G77" t="str">
         <v>0</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B78" t="str">
-        <v>Diglett's Tunnel</v>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>Larvitar</v>
+        <v>Passimian</v>
       </c>
       <c r="E78" t="str">
-        <v>38-43</v>
+        <v>35-40</v>
       </c>
       <c r="F78" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G78" t="str">
         <v>0</v>
@@ -2198,22 +2198,22 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Challenge 20</v>
+        <v/>
       </c>
       <c r="B79" t="str">
-        <v>Akala Outskirts</v>
+        <v>Captain Mallow Boss Battle</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>Gumshoos</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v>43-48</v>
+        <v/>
       </c>
       <c r="F79" t="str">
-        <v>12.50%</v>
+        <v/>
       </c>
       <c r="G79" t="str">
         <v>0</v>
@@ -2221,22 +2221,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B80" t="str">
-        <v>Akala Outskirts</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>Wingull</v>
+        <v>Zubat</v>
       </c>
       <c r="E80" t="str">
-        <v>43-48</v>
+        <v>38-43</v>
       </c>
       <c r="F80" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
       <c r="G80" t="str">
         <v>0</v>
@@ -2244,22 +2244,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B81" t="str">
-        <v>Akala Outskirts</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>Magikarp</v>
+        <v>Diglett</v>
       </c>
       <c r="E81" t="str">
-        <v>43-48</v>
+        <v>38-43</v>
       </c>
       <c r="F81" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
       <c r="G81" t="str">
         <v>0</v>
@@ -2267,22 +2267,22 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B82" t="str">
-        <v>Akala Outskirts</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>Stufful</v>
+        <v>Kecleon</v>
       </c>
       <c r="E82" t="str">
-        <v>43-48</v>
+        <v>38-43</v>
       </c>
       <c r="F82" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
       <c r="G82" t="str">
         <v>0</v>
@@ -2290,22 +2290,22 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B83" t="str">
-        <v>Akala Outskirts</v>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>Chinchou</v>
+        <v>Larvitar</v>
       </c>
       <c r="E83" t="str">
-        <v>43-48</v>
+        <v>38-43</v>
       </c>
       <c r="F83" t="str">
-        <v>12.50%</v>
+        <v>25.00%</v>
       </c>
       <c r="G83" t="str">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>Raticate</v>
+        <v>Gumshoos</v>
       </c>
       <c r="E84" t="str">
         <v>43-48</v>
@@ -2345,7 +2345,7 @@
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>Natu</v>
+        <v>Wingull</v>
       </c>
       <c r="E85" t="str">
         <v>43-48</v>
@@ -2368,7 +2368,7 @@
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>Nosepass</v>
+        <v>Magikarp</v>
       </c>
       <c r="E86" t="str">
         <v>43-48</v>
@@ -2382,22 +2382,22 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B87" t="str">
-        <v>Kahuna Olivia</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C87" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>Stufful</v>
       </c>
       <c r="E87" t="str">
-        <v/>
+        <v>43-48</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>12.50%</v>
       </c>
       <c r="G87" t="str">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B88" t="str">
-        <v>Malie City</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>Magnemite</v>
+        <v>Chinchou</v>
       </c>
       <c r="E88" t="str">
-        <v>48-53</v>
+        <v>43-48</v>
       </c>
       <c r="F88" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G88" t="str">
         <v>0</v>
@@ -2428,22 +2428,22 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B89" t="str">
-        <v>Malie City</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>Grimer</v>
+        <v>Raticate</v>
       </c>
       <c r="E89" t="str">
-        <v>48-53</v>
+        <v>43-48</v>
       </c>
       <c r="F89" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G89" t="str">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B90" t="str">
-        <v>Malie City</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>Trubbish</v>
+        <v>Natu</v>
       </c>
       <c r="E90" t="str">
-        <v>48-53</v>
+        <v>43-48</v>
       </c>
       <c r="F90" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G90" t="str">
         <v>0</v>
@@ -2474,22 +2474,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B91" t="str">
-        <v>Malie City</v>
+        <v>Akala Outskirts</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>Minccino</v>
+        <v>Nosepass</v>
       </c>
       <c r="E91" t="str">
-        <v>48-53</v>
+        <v>43-48</v>
       </c>
       <c r="F91" t="str">
-        <v>20.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G91" t="str">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Challenge 22</v>
+        <v/>
       </c>
       <c r="B92" t="str">
-        <v>Malie City</v>
+        <v>Kahuna Olivia Boss Battle</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>Masquerain</v>
+        <v/>
       </c>
       <c r="E92" t="str">
-        <v>48-53</v>
+        <v/>
       </c>
       <c r="F92" t="str">
-        <v>20.00%</v>
+        <v/>
       </c>
       <c r="G92" t="str">
         <v>0</v>
@@ -2520,22 +2520,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B93" t="str">
-        <v>Mount Hokulani</v>
+        <v>Malie City</v>
       </c>
       <c r="C93" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D93" t="str">
-        <v>Cleffa</v>
+        <v>Magnemite</v>
       </c>
       <c r="E93" t="str">
-        <v>52-57</v>
+        <v>48-53</v>
       </c>
       <c r="F93" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G93" t="str">
         <v>0</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B94" t="str">
-        <v>Mount Hokulani</v>
+        <v>Malie City</v>
       </c>
       <c r="C94" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D94" t="str">
-        <v>Elgyem</v>
+        <v>Grimer</v>
       </c>
       <c r="E94" t="str">
-        <v>52-57</v>
+        <v>48-53</v>
       </c>
       <c r="F94" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G94" t="str">
         <v>0</v>
@@ -2566,22 +2566,22 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B95" t="str">
-        <v>Mount Hokulani</v>
+        <v>Malie City</v>
       </c>
       <c r="C95" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D95" t="str">
-        <v>Beldum</v>
+        <v>Trubbish</v>
       </c>
       <c r="E95" t="str">
-        <v>52-57</v>
+        <v>48-53</v>
       </c>
       <c r="F95" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G95" t="str">
         <v>0</v>
@@ -2589,22 +2589,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B96" t="str">
-        <v>Mount Hokulani</v>
+        <v>Malie City</v>
       </c>
       <c r="C96" t="str">
-        <v>East</v>
+        <v/>
       </c>
       <c r="D96" t="str">
-        <v>Minior</v>
+        <v>Minccino</v>
       </c>
       <c r="E96" t="str">
-        <v>52-57</v>
+        <v>48-53</v>
       </c>
       <c r="F96" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
       <c r="G96" t="str">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B97" t="str">
-        <v>Captain Sophocles</v>
+        <v>Malie City</v>
       </c>
       <c r="C97" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D97" t="str">
-        <v/>
+        <v>Masquerain</v>
       </c>
       <c r="E97" t="str">
-        <v/>
+        <v>48-53</v>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>20.00%</v>
       </c>
       <c r="G97" t="str">
         <v>0</v>
@@ -2635,22 +2635,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B98" t="str">
-        <v>Haina Desert</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>Dugtrio</v>
+        <v>Cleffa</v>
       </c>
       <c r="E98" t="str">
-        <v>58-63</v>
+        <v>52-57</v>
       </c>
       <c r="F98" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G98" t="str">
         <v>0</v>
@@ -2658,22 +2658,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B99" t="str">
-        <v>Haina Desert</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>Sandile</v>
+        <v>Elgyem</v>
       </c>
       <c r="E99" t="str">
-        <v>58-63</v>
+        <v>52-57</v>
       </c>
       <c r="F99" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G99" t="str">
         <v>0</v>
@@ -2681,22 +2681,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B100" t="str">
-        <v>Haina Desert</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>Krokorok</v>
+        <v>Beldum</v>
       </c>
       <c r="E100" t="str">
-        <v>58-63</v>
+        <v>52-57</v>
       </c>
       <c r="F100" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G100" t="str">
         <v>0</v>
@@ -2704,22 +2704,22 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B101" t="str">
-        <v>Haina Desert</v>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>Staryu</v>
+        <v>Minior</v>
       </c>
       <c r="E101" t="str">
-        <v>58-63</v>
+        <v>52-57</v>
       </c>
       <c r="F101" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G101" t="str">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Challenge 25</v>
+        <v/>
       </c>
       <c r="B102" t="str">
-        <v>Haina Desert</v>
+        <v>Captain Sophocles Boss Battle</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>Sandygast</v>
+        <v/>
       </c>
       <c r="E102" t="str">
-        <v>58-63</v>
+        <v/>
       </c>
       <c r="F102" t="str">
-        <v>20.00%</v>
+        <v/>
       </c>
       <c r="G102" t="str">
         <v>0</v>
@@ -2750,22 +2750,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B103" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>Graveler</v>
+        <v>Dugtrio</v>
       </c>
       <c r="E103" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F103" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G103" t="str">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B104" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>Bruxish</v>
+        <v>Sandile</v>
       </c>
       <c r="E104" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F104" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G104" t="str">
         <v>0</v>
@@ -2796,22 +2796,22 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B105" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>Absol</v>
+        <v>Krokorok</v>
       </c>
       <c r="E105" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F105" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G105" t="str">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B106" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>Snorunt</v>
+        <v>Staryu</v>
       </c>
       <c r="E106" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F106" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G106" t="str">
         <v>0</v>
@@ -2842,22 +2842,22 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B107" t="str">
-        <v>Tapu Village</v>
+        <v>Haina Desert</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>Sandshrew</v>
+        <v>Sandygast</v>
       </c>
       <c r="E107" t="str">
-        <v>60-65</v>
+        <v>58-63</v>
       </c>
       <c r="F107" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G107" t="str">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>Vulpix</v>
+        <v>Graveler</v>
       </c>
       <c r="E108" t="str">
         <v>60-65</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B109" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>Haunter</v>
+        <v>Bruxish</v>
       </c>
       <c r="E109" t="str">
-        <v>63-68</v>
+        <v>60-65</v>
       </c>
       <c r="F109" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G109" t="str">
         <v>0</v>
@@ -2911,22 +2911,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B110" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>Klefki</v>
+        <v>Absol</v>
       </c>
       <c r="E110" t="str">
-        <v>63-68</v>
+        <v>60-65</v>
       </c>
       <c r="F110" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G110" t="str">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B111" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>Shuppet</v>
+        <v>Snorunt</v>
       </c>
       <c r="E111" t="str">
-        <v>63-68</v>
+        <v>60-65</v>
       </c>
       <c r="F111" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G111" t="str">
         <v>0</v>
@@ -2957,22 +2957,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B112" t="str">
-        <v>Thrifty Megamart</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>Boldore</v>
+        <v>Sandshrew</v>
       </c>
       <c r="E112" t="str">
-        <v>63-68</v>
+        <v>60-65</v>
       </c>
       <c r="F112" t="str">
-        <v>25.00%</v>
+        <v>16.67%</v>
       </c>
       <c r="G112" t="str">
         <v>0</v>
@@ -2980,22 +2980,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B113" t="str">
-        <v>Captain Acerola</v>
+        <v>Tapu Village</v>
       </c>
       <c r="C113" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D113" t="str">
-        <v/>
+        <v>Vulpix</v>
       </c>
       <c r="E113" t="str">
-        <v/>
+        <v>60-65</v>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>16.67%</v>
       </c>
       <c r="G113" t="str">
         <v>0</v>
@@ -3003,22 +3003,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B114" t="str">
-        <v>Kahuna Nanu</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C114" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D114" t="str">
-        <v/>
+        <v>Haunter</v>
       </c>
       <c r="E114" t="str">
-        <v/>
+        <v>63-68</v>
       </c>
       <c r="F114" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G114" t="str">
         <v>0</v>
@@ -3026,22 +3026,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B115" t="str">
-        <v>Seafolk Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>Steenee</v>
+        <v>Klefki</v>
       </c>
       <c r="E115" t="str">
-        <v>69-74</v>
+        <v>63-68</v>
       </c>
       <c r="F115" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
       <c r="G115" t="str">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B116" t="str">
-        <v>Seafolk Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>Shellos</v>
+        <v>Shuppet</v>
       </c>
       <c r="E116" t="str">
-        <v>69-74</v>
+        <v>63-68</v>
       </c>
       <c r="F116" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
       <c r="G116" t="str">
         <v>0</v>
@@ -3072,22 +3072,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B117" t="str">
-        <v>Seafolk Village</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>Dhelmise</v>
+        <v>Boldore</v>
       </c>
       <c r="E117" t="str">
-        <v>69-74</v>
+        <v>63-68</v>
       </c>
       <c r="F117" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
       <c r="G117" t="str">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B118" t="str">
-        <v>Poni Wilds</v>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>Tentacruel</v>
+        <v>Mimikyu</v>
       </c>
       <c r="E118" t="str">
-        <v>70-75</v>
+        <v>63-68</v>
       </c>
       <c r="F118" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G118" t="str">
         <v>0</v>
@@ -3118,22 +3118,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Challenge 31</v>
+        <v/>
       </c>
       <c r="B119" t="str">
-        <v>Poni Wilds</v>
+        <v>Captain Acerola Boss Battle</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>Lumineon</v>
+        <v/>
       </c>
       <c r="E119" t="str">
-        <v>70-75</v>
+        <v/>
       </c>
       <c r="F119" t="str">
-        <v>20.00%</v>
+        <v/>
       </c>
       <c r="G119" t="str">
         <v>0</v>
@@ -3141,22 +3141,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Challenge 31</v>
+        <v/>
       </c>
       <c r="B120" t="str">
-        <v>Poni Wilds</v>
+        <v>Kahuna Nanu Boss Battle</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>Lapras</v>
+        <v/>
       </c>
       <c r="E120" t="str">
-        <v>70-75</v>
+        <v/>
       </c>
       <c r="F120" t="str">
-        <v>20.00%</v>
+        <v/>
       </c>
       <c r="G120" t="str">
         <v>0</v>
@@ -3164,22 +3164,22 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B121" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>Noivern</v>
+        <v>Steenee</v>
       </c>
       <c r="E121" t="str">
-        <v>70-75</v>
+        <v>69-74</v>
       </c>
       <c r="F121" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G121" t="str">
         <v>0</v>
@@ -3187,22 +3187,22 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B122" t="str">
-        <v>Poni Wilds</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>Druddigon</v>
+        <v>Shellos</v>
       </c>
       <c r="E122" t="str">
-        <v>70-75</v>
+        <v>69-74</v>
       </c>
       <c r="F122" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G122" t="str">
         <v>0</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B123" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Seafolk Village</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>Wimpod</v>
+        <v>Dhelmise</v>
       </c>
       <c r="E123" t="str">
-        <v>72-77</v>
+        <v>69-74</v>
       </c>
       <c r="F123" t="str">
-        <v>20.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G123" t="str">
         <v>0</v>
@@ -3233,19 +3233,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B124" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>Relicanth</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E124" t="str">
-        <v>72-77</v>
+        <v>70-75</v>
       </c>
       <c r="F124" t="str">
         <v>20.00%</v>
@@ -3256,19 +3256,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B125" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>Wailmer</v>
+        <v>Lumineon</v>
       </c>
       <c r="E125" t="str">
-        <v>72-77</v>
+        <v>70-75</v>
       </c>
       <c r="F125" t="str">
         <v>20.00%</v>
@@ -3279,19 +3279,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B126" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>Carvanha</v>
+        <v>Lapras</v>
       </c>
       <c r="E126" t="str">
-        <v>72-77</v>
+        <v>70-75</v>
       </c>
       <c r="F126" t="str">
         <v>20.00%</v>
@@ -3302,19 +3302,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B127" t="str">
-        <v>Poni Breaker Coast</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>Sharpedo</v>
+        <v>Noivern</v>
       </c>
       <c r="E127" t="str">
-        <v>72-77</v>
+        <v>70-75</v>
       </c>
       <c r="F127" t="str">
         <v>20.00%</v>
@@ -3325,22 +3325,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B128" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Wilds</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>Pelipper</v>
+        <v>Druddigon</v>
       </c>
       <c r="E128" t="str">
-        <v>73-78</v>
+        <v>70-75</v>
       </c>
       <c r="F128" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G128" t="str">
         <v>0</v>
@@ -3348,22 +3348,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B129" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>Pinsir</v>
+        <v>Wimpod</v>
       </c>
       <c r="E129" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F129" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G129" t="str">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B130" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>Gastrodon</v>
+        <v>Relicanth</v>
       </c>
       <c r="E130" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F130" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G130" t="str">
         <v>0</v>
@@ -3394,22 +3394,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B131" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>Exeggcute</v>
+        <v>Wailmer</v>
       </c>
       <c r="E131" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F131" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G131" t="str">
         <v>0</v>
@@ -3417,22 +3417,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B132" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>Tropius</v>
+        <v>Carvanha</v>
       </c>
       <c r="E132" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F132" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G132" t="str">
         <v>0</v>
@@ -3440,22 +3440,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B133" t="str">
-        <v>Exeggutor Island</v>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>Exeggutor</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E133" t="str">
-        <v>73-78</v>
+        <v>72-77</v>
       </c>
       <c r="F133" t="str">
-        <v>16.67%</v>
+        <v>20.00%</v>
       </c>
       <c r="G133" t="str">
         <v>0</v>
@@ -3463,22 +3463,22 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B134" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C134" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D134" t="str">
-        <v>Machoke</v>
+        <v>Pelipper</v>
       </c>
       <c r="E134" t="str">
-        <v>75-80</v>
+        <v>73-78</v>
       </c>
       <c r="F134" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
       <c r="G134" t="str">
         <v>0</v>
@@ -3486,22 +3486,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B135" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C135" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D135" t="str">
-        <v>Mienfoo</v>
+        <v>Pinsir</v>
       </c>
       <c r="E135" t="str">
-        <v>75-80</v>
+        <v>73-78</v>
       </c>
       <c r="F135" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
       <c r="G135" t="str">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B136" t="str">
-        <v>Vast Poni Canyon</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C136" t="str">
-        <v>Outside</v>
+        <v/>
       </c>
       <c r="D136" t="str">
-        <v>Jangmo-o</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E136" t="str">
-        <v>75-80</v>
+        <v>73-78</v>
       </c>
       <c r="F136" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
       <c r="G136" t="str">
         <v>0</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B137" t="str">
-        <v>Captain Kommo-o</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C137" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D137" t="str">
-        <v/>
+        <v>Exeggcute</v>
       </c>
       <c r="E137" t="str">
-        <v/>
+        <v>73-78</v>
       </c>
       <c r="F137" t="str">
-        <v/>
+        <v>16.67%</v>
       </c>
       <c r="G137" t="str">
         <v>0</v>
@@ -3555,22 +3555,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B138" t="str">
-        <v>Captain Mina</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C138" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D138" t="str">
-        <v/>
+        <v>Tropius</v>
       </c>
       <c r="E138" t="str">
-        <v/>
+        <v>73-78</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>16.67%</v>
       </c>
       <c r="G138" t="str">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B139" t="str">
-        <v>Kahuna Hapu</v>
+        <v>Exeggutor Island</v>
       </c>
       <c r="C139" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D139" t="str">
-        <v/>
+        <v>Exeggutor</v>
       </c>
       <c r="E139" t="str">
-        <v/>
+        <v>73-78</v>
       </c>
       <c r="F139" t="str">
-        <v/>
+        <v>16.67%</v>
       </c>
       <c r="G139" t="str">
         <v>0</v>
@@ -3601,22 +3601,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B140" t="str">
-        <v>Mount Lanakila</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>Drampa</v>
+        <v>Machoke</v>
       </c>
       <c r="E140" t="str">
-        <v>82-87</v>
+        <v>75-80</v>
       </c>
       <c r="F140" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G140" t="str">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B141" t="str">
-        <v>Mount Lanakila</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>Glalie</v>
+        <v>Mienfoo</v>
       </c>
       <c r="E141" t="str">
-        <v>82-87</v>
+        <v>75-80</v>
       </c>
       <c r="F141" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G141" t="str">
         <v>0</v>
@@ -3647,22 +3647,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B142" t="str">
-        <v>Mount Lanakila</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>Sneasel</v>
+        <v>Jangmo-o</v>
       </c>
       <c r="E142" t="str">
-        <v>82-87</v>
+        <v>75-80</v>
       </c>
       <c r="F142" t="str">
-        <v>25.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G142" t="str">
         <v>0</v>
@@ -3670,22 +3670,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B143" t="str">
-        <v>Mount Lanakila</v>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>Crabominable</v>
+        <v>Hakamo-o</v>
       </c>
       <c r="E143" t="str">
-        <v>82-87</v>
+        <v>75-80</v>
       </c>
       <c r="F143" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G143" t="str">
         <v>0</v>
@@ -3696,10 +3696,10 @@
         <v/>
       </c>
       <c r="B144" t="str">
-        <v>Alola Pokemon League</v>
+        <v>Captain Kommo-o Boss Battle</v>
       </c>
       <c r="C144" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D144" t="str">
         <v/>
@@ -3719,10 +3719,10 @@
         <v/>
       </c>
       <c r="B145" t="str">
-        <v>Champion Hau</v>
+        <v>Captain Mina Boss Battle</v>
       </c>
       <c r="C145" t="str">
-        <v>Boss Battle</v>
+        <v/>
       </c>
       <c r="D145" t="str">
         <v/>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Extra Challenge A-1</v>
+        <v/>
       </c>
       <c r="B146" t="str">
-        <v>Route 6</v>
+        <v>Kahuna Hapu Boss Battle</v>
       </c>
       <c r="C146" t="str">
         <v/>
@@ -3762,22 +3762,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Extra Challenge B-3</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B147" t="str">
-        <v>Shopping Mall Antiquities</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v/>
+        <v>Drampa</v>
       </c>
       <c r="E147" t="str">
-        <v/>
+        <v>82-87</v>
       </c>
       <c r="F147" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G147" t="str">
         <v>0</v>
@@ -3785,22 +3785,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Extra Challenge C-1</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B148" t="str">
-        <v>Ruins of Conflict</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v/>
+        <v>Glalie</v>
       </c>
       <c r="E148" t="str">
-        <v/>
+        <v>82-87</v>
       </c>
       <c r="F148" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G148" t="str">
         <v>0</v>
@@ -3808,22 +3808,22 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Extra Challenge C-2</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B149" t="str">
-        <v>Ten Carat Hill</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C149" t="str">
-        <v>Deepest Cave</v>
+        <v/>
       </c>
       <c r="D149" t="str">
-        <v/>
+        <v>Sneasel</v>
       </c>
       <c r="E149" t="str">
-        <v/>
+        <v>82-87</v>
       </c>
       <c r="F149" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G149" t="str">
         <v>0</v>
@@ -3831,22 +3831,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B150" t="str">
-        <v>Poni Plains</v>
+        <v>Mount Lanakila</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v/>
+        <v>Crabominable</v>
       </c>
       <c r="E150" t="str">
-        <v/>
+        <v>82-87</v>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>25.00%</v>
       </c>
       <c r="G150" t="str">
         <v>0</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Extra Challenge D-2</v>
+        <v/>
       </c>
       <c r="B151" t="str">
-        <v>Resolution Cave</v>
+        <v>Alola Pokemon League Boss Battle</v>
       </c>
       <c r="C151" t="str">
         <v/>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Extra Challenge D-3</v>
+        <v/>
       </c>
       <c r="B152" t="str">
-        <v>Ruins of Hope</v>
+        <v>Champion Hau Boss Battle</v>
       </c>
       <c r="C152" t="str">
         <v/>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v/>
+        <v>Extra Challenge A-1</v>
       </c>
       <c r="B153" t="str">
-        <v>Route 16</v>
+        <v>Route 6</v>
       </c>
       <c r="C153" t="str">
         <v/>
@@ -3923,22 +3923,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Extra Challenge A-2</v>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="B154" t="str">
-        <v>Royal Avenue</v>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>Oricorio</v>
+        <v/>
       </c>
       <c r="E154" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F154" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
       <c r="G154" t="str">
         <v>0</v>
@@ -3946,22 +3946,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Extra Challenge A-2</v>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="B155" t="str">
-        <v>Royal Avenue</v>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>Trumbeak</v>
+        <v/>
       </c>
       <c r="E155" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F155" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
       <c r="G155" t="str">
         <v>0</v>
@@ -3969,22 +3969,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Extra Challenge A-2</v>
+        <v>Extra Challenge C-2</v>
       </c>
       <c r="B156" t="str">
-        <v>Royal Avenue</v>
+        <v>Ten Carat Hill Deepest Cave</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>Ribombee</v>
+        <v/>
       </c>
       <c r="E156" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F156" t="str">
-        <v>33.33%</v>
+        <v/>
       </c>
       <c r="G156" t="str">
         <v>0</v>
@@ -3992,22 +3992,22 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Extra Challenge A-3</v>
+        <v/>
       </c>
       <c r="B157" t="str">
-        <v>Pikachu Valley</v>
+        <v>Poni Plains</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>Pikachu</v>
+        <v/>
       </c>
       <c r="E157" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F157" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G157" t="str">
         <v>0</v>
@@ -4015,22 +4015,22 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Extra Challenge A-3</v>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="B158" t="str">
-        <v>Pikachu Valley</v>
+        <v>Resolution Cave</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>Raichu</v>
+        <v/>
       </c>
       <c r="E158" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F158" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G158" t="str">
         <v>0</v>
@@ -4038,22 +4038,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Extra Challenge A-3</v>
+        <v>Extra Challenge D-3</v>
       </c>
       <c r="B159" t="str">
-        <v>Pikachu Valley</v>
+        <v>Ruins of Hope</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>Pichu</v>
+        <v/>
       </c>
       <c r="E159" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F159" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G159" t="str">
         <v>0</v>
@@ -4061,22 +4061,22 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Extra Challenge A-3</v>
+        <v/>
       </c>
       <c r="B160" t="str">
-        <v>Pikachu Valley</v>
+        <v>Route 16</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>Magnemite</v>
+        <v/>
       </c>
       <c r="E160" t="str">
-        <v>85-90</v>
+        <v/>
       </c>
       <c r="F160" t="str">
-        <v>25.00%</v>
+        <v/>
       </c>
       <c r="G160" t="str">
         <v>0</v>
@@ -4084,22 +4084,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B161" t="str">
-        <v>Starter Depot</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C161" t="str">
         <v/>
       </c>
       <c r="D161" t="str">
-        <v>Rowlet</v>
+        <v>Oricorio</v>
       </c>
       <c r="E161" t="str">
         <v>85-90</v>
       </c>
       <c r="F161" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
       <c r="G161" t="str">
         <v>0</v>
@@ -4107,22 +4107,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B162" t="str">
-        <v>Starter Depot</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162" t="str">
-        <v>Dartrix</v>
+        <v>Trumbeak</v>
       </c>
       <c r="E162" t="str">
         <v>85-90</v>
       </c>
       <c r="F162" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
       <c r="G162" t="str">
         <v>0</v>
@@ -4130,22 +4130,22 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B163" t="str">
-        <v>Starter Depot</v>
+        <v>Royal Avenue</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163" t="str">
-        <v>Litten</v>
+        <v>Ribombee</v>
       </c>
       <c r="E163" t="str">
         <v>85-90</v>
       </c>
       <c r="F163" t="str">
-        <v>16.67%</v>
+        <v>33.33%</v>
       </c>
       <c r="G163" t="str">
         <v>0</v>
@@ -4153,22 +4153,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B164" t="str">
-        <v>Starter Depot</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164" t="str">
-        <v>Torracat</v>
+        <v>Pikachu</v>
       </c>
       <c r="E164" t="str">
         <v>85-90</v>
       </c>
       <c r="F164" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
       <c r="G164" t="str">
         <v>0</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B165" t="str">
-        <v>Starter Depot</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C165" t="str">
         <v/>
       </c>
       <c r="D165" t="str">
-        <v>Popplio</v>
+        <v>Raichu</v>
       </c>
       <c r="E165" t="str">
         <v>85-90</v>
       </c>
       <c r="F165" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
       <c r="G165" t="str">
         <v>0</v>
@@ -4199,22 +4199,22 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Extra Challenge A-4</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B166" t="str">
-        <v>Starter Depot</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v>Brionne</v>
+        <v>Pichu</v>
       </c>
       <c r="E166" t="str">
         <v>85-90</v>
       </c>
       <c r="F166" t="str">
-        <v>16.67%</v>
+        <v>25.00%</v>
       </c>
       <c r="G166" t="str">
         <v>0</v>
@@ -4222,22 +4222,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Extra Challenge B-1</v>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B167" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Pikachu Valley</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>Ledian</v>
+        <v>Magnemite</v>
       </c>
       <c r="E167" t="str">
         <v>85-90</v>
       </c>
       <c r="F167" t="str">
-        <v>33.33%</v>
+        <v>25.00%</v>
       </c>
       <c r="G167" t="str">
         <v>0</v>
@@ -4245,22 +4245,22 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Extra Challenge B-1</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B168" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168" t="str">
-        <v>Ariados</v>
+        <v>Rowlet</v>
       </c>
       <c r="E168" t="str">
         <v>85-90</v>
       </c>
       <c r="F168" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
       <c r="G168" t="str">
         <v>0</v>
@@ -4268,22 +4268,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Extra Challenge B-1</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B169" t="str">
-        <v>Ula'ula Meadow</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C169" t="str">
         <v/>
       </c>
       <c r="D169" t="str">
-        <v>Oricorio</v>
+        <v>Dartrix</v>
       </c>
       <c r="E169" t="str">
         <v>85-90</v>
       </c>
       <c r="F169" t="str">
-        <v>33.33%</v>
+        <v>16.67%</v>
       </c>
       <c r="G169" t="str">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B170" t="str">
-        <v>Blush Mountain</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>Mudbray</v>
+        <v>Litten</v>
       </c>
       <c r="E170" t="str">
         <v>85-90</v>
       </c>
       <c r="F170" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
       <c r="G170" t="str">
         <v>0</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B171" t="str">
-        <v>Blush Mountain</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>Torkoal</v>
+        <v>Torracat</v>
       </c>
       <c r="E171" t="str">
         <v>85-90</v>
       </c>
       <c r="F171" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
       <c r="G171" t="str">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B172" t="str">
-        <v>Blush Mountain</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>Togedemaru</v>
+        <v>Popplio</v>
       </c>
       <c r="E172" t="str">
         <v>85-90</v>
       </c>
       <c r="F172" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
       <c r="G172" t="str">
         <v>0</v>
@@ -4360,22 +4360,22 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B173" t="str">
-        <v>Blush Mountain</v>
+        <v>Starter Depot</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>Elekid</v>
+        <v>Brionne</v>
       </c>
       <c r="E173" t="str">
         <v>85-90</v>
       </c>
       <c r="F173" t="str">
-        <v>11.11%</v>
+        <v>16.67%</v>
       </c>
       <c r="G173" t="str">
         <v>0</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B174" t="str">
-        <v>Blush Mountain</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>Geodude</v>
+        <v>Ledian</v>
       </c>
       <c r="E174" t="str">
         <v>85-90</v>
       </c>
       <c r="F174" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
       <c r="G174" t="str">
         <v>0</v>
@@ -4406,22 +4406,22 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B175" t="str">
-        <v>Blush Mountain</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175" t="str">
-        <v>Graveler</v>
+        <v>Ariados</v>
       </c>
       <c r="E175" t="str">
         <v>85-90</v>
       </c>
       <c r="F175" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
       <c r="G175" t="str">
         <v>0</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B176" t="str">
-        <v>Blush Mountain</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C176" t="str">
         <v/>
       </c>
       <c r="D176" t="str">
-        <v>Charjabug</v>
+        <v>Oricorio</v>
       </c>
       <c r="E176" t="str">
         <v>85-90</v>
       </c>
       <c r="F176" t="str">
-        <v>11.11%</v>
+        <v>33.33%</v>
       </c>
       <c r="G176" t="str">
         <v>0</v>
@@ -4452,22 +4452,22 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Extra Challenge B-2</v>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B177" t="str">
-        <v>Blush Mountain</v>
+        <v>Ula'ula Meadow</v>
       </c>
       <c r="C177" t="str">
         <v/>
       </c>
       <c r="D177" t="str">
-        <v>Turtonator</v>
+        <v>Komala</v>
       </c>
       <c r="E177" t="str">
         <v>85-90</v>
       </c>
       <c r="F177" t="str">
-        <v>11.11%</v>
+        <v>10.00%</v>
       </c>
       <c r="G177" t="str">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>Dedenne</v>
+        <v>Mudbray</v>
       </c>
       <c r="E178" t="str">
         <v>85-90</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Extra Challenge B-4</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B179" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C179" t="str">
         <v/>
       </c>
       <c r="D179" t="str">
-        <v>Magearna</v>
+        <v>Torkoal</v>
       </c>
       <c r="E179" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F179" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
       <c r="G179" t="str">
         <v>0</v>
@@ -4521,22 +4521,22 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Extra Challenge B-4</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B180" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v>Marshadow</v>
+        <v>Togedemaru</v>
       </c>
       <c r="E180" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F180" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
       <c r="G180" t="str">
         <v>0</v>
@@ -4544,22 +4544,22 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Extra Challenge B-4</v>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B181" t="str">
-        <v>The Zenith Anomaly</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>Zeraora</v>
+        <v>Elekid</v>
       </c>
       <c r="E181" t="str">
-        <v>95-100</v>
+        <v>85-90</v>
       </c>
       <c r="F181" t="str">
-        <v>33.33%</v>
+        <v>11.11%</v>
       </c>
       <c r="G181" t="str">
         <v>0</v>
@@ -4567,22 +4567,22 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B182" t="str">
-        <v>Melemele Meadow</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>Caterpie</v>
+        <v>Geodude</v>
       </c>
       <c r="E182" t="str">
         <v>85-90</v>
       </c>
       <c r="F182" t="str">
-        <v>12.50%</v>
+        <v>11.11%</v>
       </c>
       <c r="G182" t="str">
         <v>0</v>
@@ -4590,22 +4590,22 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B183" t="str">
-        <v>Melemele Meadow</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C183" t="str">
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>Metapod</v>
+        <v>Graveler</v>
       </c>
       <c r="E183" t="str">
         <v>85-90</v>
       </c>
       <c r="F183" t="str">
-        <v>12.50%</v>
+        <v>11.11%</v>
       </c>
       <c r="G183" t="str">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B184" t="str">
-        <v>Melemele Meadow</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>Cutiefly</v>
+        <v>Charjabug</v>
       </c>
       <c r="E184" t="str">
         <v>85-90</v>
       </c>
       <c r="F184" t="str">
-        <v>12.50%</v>
+        <v>11.11%</v>
       </c>
       <c r="G184" t="str">
         <v>0</v>
@@ -4636,22 +4636,22 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B185" t="str">
-        <v>Melemele Meadow</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>Butterfree</v>
+        <v>Turtonator</v>
       </c>
       <c r="E185" t="str">
         <v>85-90</v>
       </c>
       <c r="F185" t="str">
-        <v>12.50%</v>
+        <v>11.11%</v>
       </c>
       <c r="G185" t="str">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B186" t="str">
-        <v>Melemele Meadow</v>
+        <v>Blush Mountain</v>
       </c>
       <c r="C186" t="str">
         <v/>
       </c>
       <c r="D186" t="str">
-        <v>Flabébé</v>
+        <v>Dedenne</v>
       </c>
       <c r="E186" t="str">
         <v>85-90</v>
       </c>
       <c r="F186" t="str">
-        <v>12.50%</v>
+        <v>11.11%</v>
       </c>
       <c r="G186" t="str">
         <v>0</v>
@@ -4682,22 +4682,22 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B187" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>Petilil</v>
+        <v>Magearna</v>
       </c>
       <c r="E187" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F187" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
       <c r="G187" t="str">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v/>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B188" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>Cottonee</v>
+        <v>Marshadow</v>
       </c>
       <c r="E188" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F188" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
       <c r="G188" t="str">
         <v>0</v>
@@ -4728,22 +4728,22 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B189" t="str">
-        <v>Melemele Meadow</v>
+        <v>The Zenith Anomaly</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189" t="str">
-        <v>Phantump</v>
+        <v>Zeraora</v>
       </c>
       <c r="E189" t="str">
-        <v>85-90</v>
+        <v>95-100</v>
       </c>
       <c r="F189" t="str">
-        <v>12.50%</v>
+        <v>33.33%</v>
       </c>
       <c r="G189" t="str">
         <v>0</v>
@@ -4751,22 +4751,22 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Extra Challenge C-3</v>
+        <v/>
       </c>
       <c r="B190" t="str">
-        <v>Kala'e Bay</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190" t="str">
-        <v>Shellder</v>
+        <v>Caterpie</v>
       </c>
       <c r="E190" t="str">
         <v>85-90</v>
       </c>
       <c r="F190" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
       <c r="G190" t="str">
         <v>0</v>
@@ -4774,22 +4774,22 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Extra Challenge C-3</v>
+        <v/>
       </c>
       <c r="B191" t="str">
-        <v>Kala'e Bay</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191" t="str">
-        <v>Slowpoke</v>
+        <v>Metapod</v>
       </c>
       <c r="E191" t="str">
         <v>85-90</v>
       </c>
       <c r="F191" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
       <c r="G191" t="str">
         <v>0</v>
@@ -4797,22 +4797,22 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Extra Challenge C-3</v>
+        <v/>
       </c>
       <c r="B192" t="str">
-        <v>Kala'e Bay</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C192" t="str">
         <v/>
       </c>
       <c r="D192" t="str">
-        <v>Finneon</v>
+        <v>Cutiefly</v>
       </c>
       <c r="E192" t="str">
         <v>85-90</v>
       </c>
       <c r="F192" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
       <c r="G192" t="str">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Extra Challenge C-4</v>
+        <v/>
       </c>
       <c r="B193" t="str">
-        <v>Sacred Shrine</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193" t="str">
-        <v>Tapu Koko</v>
+        <v>Butterfree</v>
       </c>
       <c r="E193" t="str">
-        <v>100</v>
+        <v>85-90</v>
       </c>
       <c r="F193" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G193" t="str">
         <v>0</v>
@@ -4843,22 +4843,22 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Extra Challenge C-4</v>
+        <v/>
       </c>
       <c r="B194" t="str">
-        <v>Sacred Shrine</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v>Tapu Lele</v>
+        <v>Flabébé</v>
       </c>
       <c r="E194" t="str">
-        <v>100</v>
+        <v>85-90</v>
       </c>
       <c r="F194" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G194" t="str">
         <v>0</v>
@@ -4866,22 +4866,22 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Extra Challenge C-4</v>
+        <v/>
       </c>
       <c r="B195" t="str">
-        <v>Sacred Shrine</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>Tapu Bulu</v>
+        <v>Petilil</v>
       </c>
       <c r="E195" t="str">
-        <v>100</v>
+        <v>85-90</v>
       </c>
       <c r="F195" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G195" t="str">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Extra Challenge C-4</v>
+        <v/>
       </c>
       <c r="B196" t="str">
-        <v>Sacred Shrine</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C196" t="str">
         <v/>
       </c>
       <c r="D196" t="str">
-        <v>Tapu Fini</v>
+        <v>Cottonee</v>
       </c>
       <c r="E196" t="str">
-        <v>100</v>
+        <v>85-90</v>
       </c>
       <c r="F196" t="str">
-        <v>25.00%</v>
+        <v>12.50%</v>
       </c>
       <c r="G196" t="str">
         <v>0</v>
@@ -4912,22 +4912,22 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Extra Challenge D-1</v>
+        <v/>
       </c>
       <c r="B197" t="str">
-        <v>Poni Coast</v>
+        <v>Melemele Meadow</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197" t="str">
-        <v>Dugtrio</v>
+        <v>Phantump</v>
       </c>
       <c r="E197" t="str">
         <v>85-90</v>
       </c>
       <c r="F197" t="str">
-        <v>33.33%</v>
+        <v>12.50%</v>
       </c>
       <c r="G197" t="str">
         <v>0</v>
@@ -4935,16 +4935,16 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Extra Challenge D-1</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B198" t="str">
-        <v>Poni Coast</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198" t="str">
-        <v>Gastrodon</v>
+        <v>Shellder</v>
       </c>
       <c r="E198" t="str">
         <v>85-90</v>
@@ -4958,16 +4958,16 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Extra Challenge D-1</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B199" t="str">
-        <v>Poni Coast</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C199" t="str">
         <v/>
       </c>
       <c r="D199" t="str">
-        <v>Exeggcute</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E199" t="str">
         <v>85-90</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B200" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Kala'e Bay</v>
       </c>
       <c r="C200" t="str">
         <v/>
       </c>
       <c r="D200" t="str">
-        <v>Nihilego</v>
+        <v>Finneon</v>
       </c>
       <c r="E200" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F200" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G200" t="str">
         <v>0</v>
@@ -5004,22 +5004,22 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B201" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v>Buzzwole</v>
+        <v>Tapu Koko</v>
       </c>
       <c r="E201" t="str">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F201" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G201" t="str">
         <v>0</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B202" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>Pheromosa</v>
+        <v>Tapu Lele</v>
       </c>
       <c r="E202" t="str">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F202" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G202" t="str">
         <v>0</v>
@@ -5050,22 +5050,22 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B203" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C203" t="str">
         <v/>
       </c>
       <c r="D203" t="str">
-        <v>Xurkitree</v>
+        <v>Tapu Bulu</v>
       </c>
       <c r="E203" t="str">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F203" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G203" t="str">
         <v>0</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B204" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Sacred Shrine</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204" t="str">
-        <v>Celesteela</v>
+        <v>Tapu Fini</v>
       </c>
       <c r="E204" t="str">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F204" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
       <c r="G204" t="str">
         <v>0</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B205" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205" t="str">
-        <v>Kartana</v>
+        <v>Dugtrio</v>
       </c>
       <c r="E205" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F205" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G205" t="str">
         <v>0</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B206" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
       <c r="D206" t="str">
-        <v>Guzzlord</v>
+        <v>Gastrodon</v>
       </c>
       <c r="E206" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F206" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G206" t="str">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Extra Challenge D-4</v>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B207" t="str">
-        <v>The Interdimensional Rift</v>
+        <v>Poni Coast</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207" t="str">
-        <v>Poipole</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E207" t="str">
-        <v>110</v>
+        <v>85-90</v>
       </c>
       <c r="F207" t="str">
-        <v>10.00%</v>
+        <v>33.33%</v>
       </c>
       <c r="G207" t="str">
         <v>0</v>
@@ -5174,7 +5174,7 @@
         <v/>
       </c>
       <c r="D208" t="str">
-        <v>Stakataka</v>
+        <v>Nihilego</v>
       </c>
       <c r="E208" t="str">
         <v>110</v>
@@ -5197,7 +5197,7 @@
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>Blacephalon</v>
+        <v>Buzzwole</v>
       </c>
       <c r="E209" t="str">
         <v>110</v>
@@ -5211,22 +5211,22 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Extra Challenge E-1</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B210" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C210" t="str">
-        <v>Labs</v>
+        <v/>
       </c>
       <c r="D210" t="str">
-        <v>Type: Null</v>
+        <v>Pheromosa</v>
       </c>
       <c r="E210" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F210" t="str">
-        <v>50.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G210" t="str">
         <v>0</v>
@@ -5234,22 +5234,22 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Extra Challenge E-1</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B211" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C211" t="str">
-        <v>Labs</v>
+        <v/>
       </c>
       <c r="D211" t="str">
-        <v>Porygon</v>
+        <v>Xurkitree</v>
       </c>
       <c r="E211" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F211" t="str">
-        <v>50.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G211" t="str">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Extra Challenge E-2</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B212" t="str">
-        <v>Aether Paradise</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C212" t="str">
-        <v>Secret Lab</v>
+        <v/>
       </c>
       <c r="D212" t="str">
-        <v>Silvally</v>
+        <v>Celesteela</v>
       </c>
       <c r="E212" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F212" t="str">
-        <v>100.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G212" t="str">
         <v>0</v>
@@ -5280,22 +5280,22 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Extra Challenge E-3</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B213" t="str">
-        <v>Lake of the Sunne</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213" t="str">
-        <v>Golbat</v>
+        <v>Kartana</v>
       </c>
       <c r="E213" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F213" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
       <c r="G213" t="str">
         <v>0</v>
@@ -5303,22 +5303,22 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Extra Challenge E-3</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B214" t="str">
-        <v>Lake of the Sunne</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214" t="str">
-        <v>Gastly</v>
+        <v>Guzzlord</v>
       </c>
       <c r="E214" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F214" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
       <c r="G214" t="str">
         <v>0</v>
@@ -5326,22 +5326,22 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Extra Challenge E-3</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B215" t="str">
-        <v>Lake of the Sunne</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v>Haunter</v>
+        <v>Poipole</v>
       </c>
       <c r="E215" t="str">
-        <v>85-90</v>
+        <v>110</v>
       </c>
       <c r="F215" t="str">
-        <v>33.33%</v>
+        <v>10.00%</v>
       </c>
       <c r="G215" t="str">
         <v>0</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Extra Challenge E-4</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B216" t="str">
-        <v>Obsidian Sphere</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>Cosmog</v>
+        <v>Stakataka</v>
       </c>
       <c r="E216" t="str">
         <v>110</v>
       </c>
       <c r="F216" t="str">
-        <v>60.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G216" t="str">
         <v>0</v>
@@ -5372,22 +5372,22 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Extra Challenge E-4</v>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B217" t="str">
-        <v>Obsidian Sphere</v>
+        <v>The Interdimensional Rift</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217" t="str">
-        <v>Cosmoem</v>
+        <v>Blacephalon</v>
       </c>
       <c r="E217" t="str">
         <v>110</v>
       </c>
       <c r="F217" t="str">
-        <v>40.00%</v>
+        <v>10.00%</v>
       </c>
       <c r="G217" t="str">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Extra Challenge E-5</v>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B218" t="str">
-        <v>Obsidian Tesseract</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218" t="str">
-        <v>Solgaleo</v>
+        <v>Type: Null</v>
       </c>
       <c r="E218" t="str">
-        <v>120</v>
+        <v>85-90</v>
       </c>
       <c r="F218" t="str">
-        <v>33.33%</v>
+        <v>50.00%</v>
       </c>
       <c r="G218" t="str">
         <v>0</v>
@@ -5418,22 +5418,22 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Extra Challenge E-5</v>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B219" t="str">
-        <v>Obsidian Tesseract</v>
+        <v>Aether Paradise Labs</v>
       </c>
       <c r="C219" t="str">
         <v/>
       </c>
       <c r="D219" t="str">
-        <v>Lunala</v>
+        <v>Porygon</v>
       </c>
       <c r="E219" t="str">
-        <v>120</v>
+        <v>85-90</v>
       </c>
       <c r="F219" t="str">
-        <v>33.33%</v>
+        <v>50.00%</v>
       </c>
       <c r="G219" t="str">
         <v>0</v>
@@ -5441,30 +5441,237 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
+        <v>Extra Challenge E-1</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Aether Paradise Labs</v>
+      </c>
+      <c r="C220" t="str">
+        <v/>
+      </c>
+      <c r="D220" t="str">
+        <v>Meltan</v>
+      </c>
+      <c r="E220" t="str">
+        <v>85-90</v>
+      </c>
+      <c r="F220" t="str">
+        <v>10.00%</v>
+      </c>
+      <c r="G220" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Extra Challenge E-2</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Aether Paradise Secret Lab</v>
+      </c>
+      <c r="C221" t="str">
+        <v/>
+      </c>
+      <c r="D221" t="str">
+        <v>Silvally</v>
+      </c>
+      <c r="E221" t="str">
+        <v>85-90</v>
+      </c>
+      <c r="F221" t="str">
+        <v>100.00%</v>
+      </c>
+      <c r="G221" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Extra Challenge E-3</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Lake of the Sunne</v>
+      </c>
+      <c r="C222" t="str">
+        <v/>
+      </c>
+      <c r="D222" t="str">
+        <v>Golbat</v>
+      </c>
+      <c r="E222" t="str">
+        <v>85-90</v>
+      </c>
+      <c r="F222" t="str">
+        <v>33.33%</v>
+      </c>
+      <c r="G222" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Extra Challenge E-3</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Lake of the Sunne</v>
+      </c>
+      <c r="C223" t="str">
+        <v/>
+      </c>
+      <c r="D223" t="str">
+        <v>Gastly</v>
+      </c>
+      <c r="E223" t="str">
+        <v>85-90</v>
+      </c>
+      <c r="F223" t="str">
+        <v>33.33%</v>
+      </c>
+      <c r="G223" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>Extra Challenge E-3</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Lake of the Sunne</v>
+      </c>
+      <c r="C224" t="str">
+        <v/>
+      </c>
+      <c r="D224" t="str">
+        <v>Haunter</v>
+      </c>
+      <c r="E224" t="str">
+        <v>85-90</v>
+      </c>
+      <c r="F224" t="str">
+        <v>33.33%</v>
+      </c>
+      <c r="G224" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Extra Challenge E-4</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="C225" t="str">
+        <v/>
+      </c>
+      <c r="D225" t="str">
+        <v>Cosmog</v>
+      </c>
+      <c r="E225" t="str">
+        <v>110</v>
+      </c>
+      <c r="F225" t="str">
+        <v>60.00%</v>
+      </c>
+      <c r="G225" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Extra Challenge E-4</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Obsidian Sphere</v>
+      </c>
+      <c r="C226" t="str">
+        <v/>
+      </c>
+      <c r="D226" t="str">
+        <v>Cosmoem</v>
+      </c>
+      <c r="E226" t="str">
+        <v>110</v>
+      </c>
+      <c r="F226" t="str">
+        <v>40.00%</v>
+      </c>
+      <c r="G226" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
         <v>Extra Challenge E-5</v>
       </c>
-      <c r="B220" t="str">
+      <c r="B227" t="str">
         <v>Obsidian Tesseract</v>
       </c>
-      <c r="C220" t="str">
-        <v/>
-      </c>
-      <c r="D220" t="str">
+      <c r="C227" t="str">
+        <v/>
+      </c>
+      <c r="D227" t="str">
+        <v>Solgaleo</v>
+      </c>
+      <c r="E227" t="str">
+        <v>120</v>
+      </c>
+      <c r="F227" t="str">
+        <v>33.33%</v>
+      </c>
+      <c r="G227" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>Extra Challenge E-5</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Obsidian Tesseract</v>
+      </c>
+      <c r="C228" t="str">
+        <v/>
+      </c>
+      <c r="D228" t="str">
+        <v>Lunala</v>
+      </c>
+      <c r="E228" t="str">
+        <v>120</v>
+      </c>
+      <c r="F228" t="str">
+        <v>33.33%</v>
+      </c>
+      <c r="G228" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>Extra Challenge E-5</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Obsidian Tesseract</v>
+      </c>
+      <c r="C229" t="str">
+        <v/>
+      </c>
+      <c r="D229" t="str">
         <v>Necrozma</v>
       </c>
-      <c r="E220" t="str">
+      <c r="E229" t="str">
         <v>120</v>
       </c>
-      <c r="F220" t="str">
+      <c r="F229" t="str">
         <v>33.33%</v>
       </c>
-      <c r="G220" t="str">
+      <c r="G229" t="str">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G220"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G229"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5500,7 +5707,7 @@
         <v>Challenge 2</v>
       </c>
       <c r="B3" t="str">
-        <v>Catch 3 Dark type Pokemon in Route 1 Hau'oli Outskirts</v>
+        <v>Catch 3 Dark type Pokemon</v>
       </c>
       <c r="C3" t="str">
         <v>Unlocks Route 2 North</v>
@@ -5511,7 +5718,7 @@
         <v>Challenge 3</v>
       </c>
       <c r="B4" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 2 North</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity</v>
       </c>
       <c r="C4" t="str">
         <v>Unlocks Captain Ilima</v>
@@ -5533,7 +5740,7 @@
         <v>Challenge 5</v>
       </c>
       <c r="B6" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Hau'oli Cemetery</v>
+        <v>Catch 2 Pokemon of Rare or better rarity</v>
       </c>
       <c r="C6" t="str">
         <v>Unlocks Ten Carat Hill Farthest Hollow</v>
@@ -5544,7 +5751,7 @@
         <v>Challenge 6</v>
       </c>
       <c r="B7" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Ten Carat Hill Farthest Hollow</v>
+        <v>Catch 1 Pokemon of Epic or better rarity</v>
       </c>
       <c r="C7" t="str">
         <v>Unlocks Seaward Cave</v>
@@ -5555,7 +5762,7 @@
         <v>Challenge 7</v>
       </c>
       <c r="B8" t="str">
-        <v>Defeat 5 specific Water type Pokemon</v>
+        <v>Defeat 5 specific Pokemon</v>
       </c>
       <c r="C8" t="str">
         <v>Unlocks Kahuna Hala</v>
@@ -5588,7 +5795,7 @@
         <v>Challenge 10</v>
       </c>
       <c r="B11" t="str">
-        <v>Interact with Daycare</v>
+        <v>Interact with Daycare NPC</v>
       </c>
       <c r="C11" t="str">
         <v>Unlocks Route 5</v>
@@ -5599,7 +5806,7 @@
         <v>Challenge 11</v>
       </c>
       <c r="B12" t="str">
-        <v>Catch 2 specific Pokemon species in Route 5</v>
+        <v>Catch 2 specific Pokemon species</v>
       </c>
       <c r="C12" t="str">
         <v>Unlocks Captain Lana</v>
@@ -5643,7 +5850,7 @@
         <v>Challenge 15</v>
       </c>
       <c r="B16" t="str">
-        <v>Catch 3 Water type Pokemon in Route 7</v>
+        <v>Catch 3 Water type Pokemon</v>
       </c>
       <c r="C16" t="str">
         <v>Unlocks Route 8 Fossil Restoration Center Part 1</v>
@@ -5654,7 +5861,7 @@
         <v>Challenge 16</v>
       </c>
       <c r="B17" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Route 8 Fossil Restoration Center Part 1</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity</v>
       </c>
       <c r="C17" t="str">
         <v>Unlocks Lush Jungle North</v>
@@ -5665,7 +5872,7 @@
         <v>Challenge 17</v>
       </c>
       <c r="B18" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Lush Jungle North</v>
+        <v>Catch 1 Pokemon of Epic or better rarity</v>
       </c>
       <c r="C18" t="str">
         <v>Unlocks Lush Jungle East Cave</v>
@@ -5676,7 +5883,7 @@
         <v>Challenge 18</v>
       </c>
       <c r="B19" t="str">
-        <v>Defeat 5 specific Poison type Pokemon</v>
+        <v>Defeat 5 specific Pokemon</v>
       </c>
       <c r="C19" t="str">
         <v>Unlocks Captain Mallow</v>
@@ -5709,7 +5916,7 @@
         <v>Challenge 21</v>
       </c>
       <c r="B22" t="str">
-        <v>Catch 2 specific Pokemon species in Akala Outskirts</v>
+        <v>Catch 2 specific Pokemon species</v>
       </c>
       <c r="C22" t="str">
         <v>Unlocks Kahuna Olivia</v>
@@ -5742,7 +5949,7 @@
         <v>Challenge 24</v>
       </c>
       <c r="B25" t="str">
-        <v>Catch 3 Fairy type Pokemon in Mount Hokulani East</v>
+        <v>Catch 3 Fairy type Pokemon</v>
       </c>
       <c r="C25" t="str">
         <v>Unlocks Captain Sophocles</v>
@@ -5764,7 +5971,7 @@
         <v>Challenge 26</v>
       </c>
       <c r="B27" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Haina Desert</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity</v>
       </c>
       <c r="C27" t="str">
         <v>Unlocks Tapu Village</v>
@@ -5775,7 +5982,7 @@
         <v>Challenge 27</v>
       </c>
       <c r="B28" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Tapu Village</v>
+        <v>Catch 2 Pokemon of Rare or better rarity</v>
       </c>
       <c r="C28" t="str">
         <v>Unlocks Thrifty Megamart</v>
@@ -5786,7 +5993,7 @@
         <v>Challenge 28</v>
       </c>
       <c r="B29" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Thrifty Megamart</v>
+        <v>Catch 1 Pokemon of Epic or better rarity</v>
       </c>
       <c r="C29" t="str">
         <v>Unlocks Captain Acerola</v>
@@ -5819,7 +6026,7 @@
         <v>Challenge 31</v>
       </c>
       <c r="B32" t="str">
-        <v>Defeat 5 specific Grass type Pokemon</v>
+        <v>Defeat 5 specific Pokemon</v>
       </c>
       <c r="C32" t="str">
         <v>Unlocks Poni Wilds</v>
@@ -5841,7 +6048,7 @@
         <v>Challenge 33</v>
       </c>
       <c r="B34" t="str">
-        <v>Catch 2 specific Pokemon species in Poni Breaker Coast</v>
+        <v>Catch 2 specific Pokemon species</v>
       </c>
       <c r="C34" t="str">
         <v>Unlocks Exeggutor Island</v>
@@ -5863,7 +6070,7 @@
         <v>Challenge 35</v>
       </c>
       <c r="B36" t="str">
-        <v>Catch 3 Fighting type Pokemon in Vast Poni Canyon Outside</v>
+        <v>Catch 3 Fighting type Pokemon</v>
       </c>
       <c r="C36" t="str">
         <v>Unlocks Captain Kommo-o</v>
@@ -5907,7 +6114,7 @@
         <v>Challenge 39</v>
       </c>
       <c r="B40" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Mount Lanakila</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity</v>
       </c>
       <c r="C40" t="str">
         <v>Unlocks Alola Pokemon League</v>
@@ -5918,7 +6125,7 @@
         <v>Challenge 40</v>
       </c>
       <c r="B41" t="str">
-        <v>Defeat Alola Pokemon League</v>
+        <v>Defeat Alola Pokemon League / Champion</v>
       </c>
       <c r="C41" t="str">
         <v>Unlocks Champion Hau</v>
@@ -5951,7 +6158,7 @@
         <v>Extra Challenge A-3</v>
       </c>
       <c r="B44" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Royal Avenue</v>
+        <v>Catch 2 Pokemon of Rare or better rarity</v>
       </c>
       <c r="C44" t="str">
         <v>Unlocks Pikachu Valley</v>
@@ -5962,7 +6169,7 @@
         <v>Extra Challenge A-4</v>
       </c>
       <c r="B45" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Pikachu Valley</v>
+        <v>Catch 1 Pokemon of Epic or better rarity</v>
       </c>
       <c r="C45" t="str">
         <v>Unlocks Starter Depot</v>
@@ -5973,7 +6180,7 @@
         <v>Extra Challenge B-1</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat Champion Hau</v>
+        <v>Defeat Alola Pokemon League / Champion</v>
       </c>
       <c r="C46" t="str">
         <v>Unlocks Ula'ula Meadow</v>
@@ -5984,7 +6191,7 @@
         <v>Extra Challenge B-2</v>
       </c>
       <c r="B47" t="str">
-        <v>Defeat 5 specific Bug type Pokemon</v>
+        <v>Defeat 5 specific Pokemon</v>
       </c>
       <c r="C47" t="str">
         <v>Unlocks Blush Mountain</v>
@@ -6017,7 +6224,7 @@
         <v>Extra Challenge B-5</v>
       </c>
       <c r="B50" t="str">
-        <v>Catch 1 Magearna 1 Marshadow 1 Zeraora</v>
+        <v>Catch specific species</v>
       </c>
       <c r="C50" t="str">
         <v>1 Masterball</v>
@@ -6028,7 +6235,7 @@
         <v>Extra Challenge C-1</v>
       </c>
       <c r="B51" t="str">
-        <v>Catch 2 specific Pokemon species in Melemele Meadow</v>
+        <v>Catch 2 specific Pokemon species</v>
       </c>
       <c r="C51" t="str">
         <v>Unlocks Ruins of Conflict</v>
@@ -6072,7 +6279,7 @@
         <v>Extra Challenge C-5</v>
       </c>
       <c r="B55" t="str">
-        <v>Catch 1 Tapu Koko 1 Tapu Lele 1 Tapu Bulu 1 Tapu Fini</v>
+        <v>Catch specific species</v>
       </c>
       <c r="C55" t="str">
         <v>2 Masterball</v>
@@ -6094,7 +6301,7 @@
         <v>Extra Challenge D-2</v>
       </c>
       <c r="B57" t="str">
-        <v>Catch 3 Normal type Pokemon in Poni Coast</v>
+        <v>Catch 3 Normal type Pokemon</v>
       </c>
       <c r="C57" t="str">
         <v>Unlocks Resolution Cave</v>
@@ -6149,7 +6356,7 @@
         <v>Extra Challenge E-2</v>
       </c>
       <c r="B62" t="str">
-        <v>Catch 5 Pokemon of Uncommon or better rarity in Aether Paradise Labs</v>
+        <v>Catch 5 Pokemon of Uncommon or better rarity</v>
       </c>
       <c r="C62" t="str">
         <v>Unlocks Aether Paradise Secret Lab</v>
@@ -6160,7 +6367,7 @@
         <v>Extra Challenge E-3</v>
       </c>
       <c r="B63" t="str">
-        <v>Catch 2 Pokemon of Rare or better rarity in Aether Paradise Secret Lab</v>
+        <v>Catch 2 Pokemon of Rare or better rarity</v>
       </c>
       <c r="C63" t="str">
         <v>Unlocks Lake of the Sunne</v>
@@ -6171,7 +6378,7 @@
         <v>Extra Challenge E-4</v>
       </c>
       <c r="B64" t="str">
-        <v>Catch 1 Epic rarity Pokemon in Lake of the Sunne</v>
+        <v>Catch 1 Pokemon of Epic or better rarity</v>
       </c>
       <c r="C64" t="str">
         <v>Unlocks Obsidian Sphere</v>
@@ -6182,7 +6389,7 @@
         <v>Extra Challenge E-5</v>
       </c>
       <c r="B65" t="str">
-        <v>Catch 1 Cosmog 1 Cosmoem</v>
+        <v>Catch specific species</v>
       </c>
       <c r="C65" t="str">
         <v>Unlocks Obsidian Tesseract</v>
@@ -6193,7 +6400,7 @@
         <v>Extra Challenge E-6</v>
       </c>
       <c r="B66" t="str">
-        <v>Catch 1 Necrozma 1 Cosmog 1 Cosmoem</v>
+        <v>Catch specific species</v>
       </c>
       <c r="C66" t="str">
         <v>2 Masterball</v>
@@ -6208,7 +6415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6260,31 +6467,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Crabrawler</v>
+        <v>Toxapex</v>
       </c>
       <c r="B7" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Rockruff</v>
+        <v>Mudsdale</v>
       </c>
       <c r="B8" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Wishiwashi</v>
+        <v>Araquanid</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Toxapex</v>
+        <v>Lurantis</v>
       </c>
       <c r="B10" t="str">
         <v>Evolve</v>
@@ -6292,7 +6499,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mudsdale</v>
+        <v>Shiinotic</v>
       </c>
       <c r="B11" t="str">
         <v>Evolve</v>
@@ -6300,23 +6507,23 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dewpider</v>
+        <v>Salazzle</v>
       </c>
       <c r="B12" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Araquanid</v>
+        <v>Bewear</v>
       </c>
       <c r="B13" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lurantis</v>
+        <v>Tsareena</v>
       </c>
       <c r="B14" t="str">
         <v>Evolve</v>
@@ -6324,23 +6531,23 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Morelull</v>
+        <v>Golisopod</v>
       </c>
       <c r="B15" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Shiinotic</v>
+        <v>Palossand</v>
       </c>
       <c r="B16" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Salazzle</v>
+        <v>Kommo-o</v>
       </c>
       <c r="B17" t="str">
         <v>Evolve</v>
@@ -6348,7 +6555,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Bewear</v>
+        <v>Naganadel</v>
       </c>
       <c r="B18" t="str">
         <v>Evolve</v>
@@ -6356,87 +6563,15 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tsareena</v>
+        <v>Melmetal</v>
       </c>
       <c r="B19" t="str">
         <v>Evolve</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Golisopod</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Palossand</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Komala</v>
-      </c>
-      <c r="B22" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Mimikyu</v>
-      </c>
-      <c r="B23" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Hakamo-o</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Kommo-o</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2xEvolution</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Naganadel</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Meltan</v>
-      </c>
-      <c r="B27" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Melmetal</v>
-      </c>
-      <c r="B28" t="str">
-        <v>No</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/7_Alola_Data.xlsx
+++ b/7_Alola_Data.xlsx
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>Ok</v>
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>Ok</v>
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v>Ok</v>
@@ -574,7 +574,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v>Ok</v>
@@ -612,7 +612,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v>Ok</v>
@@ -650,7 +650,7 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>Ok</v>
@@ -688,7 +688,7 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>Ok</v>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H9" t="str">
         <v>Ok</v>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H10" t="str">
         <v>Ok</v>
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H11" t="str">
         <v>Ok</v>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>Ok</v>
@@ -878,7 +878,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>Ok</v>
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>Ok</v>
@@ -954,7 +954,7 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>Ok</v>
@@ -992,7 +992,7 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>Ok</v>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>Ok</v>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>Ok</v>
@@ -1106,7 +1106,7 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>Ok</v>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>Ok</v>
@@ -1182,7 +1182,7 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>Ok</v>
@@ -1258,7 +1258,7 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>Ok</v>
@@ -1296,7 +1296,7 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H24" t="str">
         <v>Ok</v>
@@ -1334,7 +1334,7 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H25" t="str">
         <v>Ok</v>
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>Ok</v>
@@ -1410,7 +1410,7 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>Ok</v>
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>NONONO</v>
@@ -1486,7 +1486,7 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>Ok</v>
@@ -1524,7 +1524,7 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>Ok</v>
@@ -1562,7 +1562,7 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>Ok</v>
@@ -1600,7 +1600,7 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v>Ok</v>
@@ -1638,7 +1638,7 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v>Ok</v>
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v>Ok</v>
@@ -1714,7 +1714,7 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v>Ok</v>
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H37" t="str">
         <v>Ok</v>
@@ -1828,7 +1828,7 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H38" t="str">
         <v>Ok</v>
@@ -1866,7 +1866,7 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v>Ok</v>
@@ -1904,7 +1904,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>Ok</v>
@@ -1980,7 +1980,7 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v>Ok</v>
@@ -2018,7 +2018,7 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>Ok</v>
@@ -2056,7 +2056,7 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H44" t="str">
         <v>Ok</v>
@@ -2094,7 +2094,7 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H45" t="str">
         <v>Ok</v>
@@ -2170,7 +2170,7 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v>Ok</v>
@@ -2208,7 +2208,7 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H48" t="str">
         <v>Ok</v>
@@ -2246,7 +2246,7 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>Ok</v>
@@ -2322,7 +2322,7 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>Ok</v>
@@ -2360,7 +2360,7 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v>Ok</v>
@@ -2398,7 +2398,7 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>Ok</v>
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>Ok</v>
@@ -2474,7 +2474,7 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v>Ok</v>
@@ -2512,7 +2512,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v>Ok</v>
@@ -2550,7 +2550,7 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v>Ok</v>
@@ -2588,7 +2588,7 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v>Ok</v>
@@ -2626,7 +2626,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>Ok</v>
@@ -2664,7 +2664,7 @@
         <v/>
       </c>
       <c r="G60" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v>Ok</v>
@@ -2702,7 +2702,7 @@
         <v/>
       </c>
       <c r="G61" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v>Ok</v>
@@ -2740,7 +2740,7 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H62" t="str">
         <v>Ok</v>
@@ -2778,7 +2778,7 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H63" t="str">
         <v>Ok</v>
@@ -2816,7 +2816,7 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H64" t="str">
         <v>Ok</v>
@@ -2854,7 +2854,7 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H65" t="str">
         <v>Ok</v>
@@ -2892,7 +2892,7 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v>Ok</v>
@@ -2930,7 +2930,7 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H67" t="str">
         <v>Ok</v>
@@ -2968,7 +2968,7 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H68" t="str">
         <v>Ok</v>
@@ -3006,7 +3006,7 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H69" t="str">
         <v>Ok</v>
@@ -3044,7 +3044,7 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H70" t="str">
         <v>Ok</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H71" t="str">
         <v>Ok</v>
@@ -3120,7 +3120,7 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H72" t="str">
         <v>Ok</v>
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H73" t="str">
         <v>Ok</v>
@@ -3196,7 +3196,7 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H74" t="str">
         <v>Ok</v>
@@ -3234,7 +3234,7 @@
         <v/>
       </c>
       <c r="G75" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H75" t="str">
         <v>Ok</v>
@@ -3272,7 +3272,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H76" t="str">
         <v>Ok</v>
@@ -3310,7 +3310,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H77" t="str">
         <v>Ok</v>
@@ -3348,7 +3348,7 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H78" t="str">
         <v>Ok</v>
@@ -3424,7 +3424,7 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H80" t="str">
         <v>Ok</v>
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H81" t="str">
         <v>Ok</v>
@@ -3500,7 +3500,7 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H82" t="str">
         <v>Ok</v>
@@ -3538,7 +3538,7 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H83" t="str">
         <v>Ok</v>
@@ -3576,7 +3576,7 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H84" t="str">
         <v>Ok</v>
@@ -3614,7 +3614,7 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H85" t="str">
         <v>Ok</v>
@@ -3652,7 +3652,7 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H86" t="str">
         <v>Ok</v>
@@ -3690,7 +3690,7 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H87" t="str">
         <v>Ok</v>
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H88" t="str">
         <v>Ok</v>
@@ -3766,7 +3766,7 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H89" t="str">
         <v>Ok</v>
@@ -3804,7 +3804,7 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H90" t="str">
         <v>Ok</v>
@@ -3842,7 +3842,7 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H91" t="str">
         <v>Ok</v>
@@ -3918,7 +3918,7 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H93" t="str">
         <v>Ok</v>
@@ -3956,7 +3956,7 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H94" t="str">
         <v>Ok</v>
@@ -3994,7 +3994,7 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H95" t="str">
         <v>Ok</v>
@@ -4032,7 +4032,7 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H96" t="str">
         <v>Ok</v>
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H97" t="str">
         <v>Ok</v>
@@ -4108,7 +4108,7 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H98" t="str">
         <v>Ok</v>
@@ -4146,7 +4146,7 @@
         <v/>
       </c>
       <c r="G99" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H99" t="str">
         <v>Ok</v>
@@ -4184,7 +4184,7 @@
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H100" t="str">
         <v>Ok</v>
@@ -4222,7 +4222,7 @@
         <v/>
       </c>
       <c r="G101" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H101" t="str">
         <v>Ok</v>
@@ -4298,7 +4298,7 @@
         <v/>
       </c>
       <c r="G103" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H103" t="str">
         <v>Ok</v>
@@ -4336,7 +4336,7 @@
         <v/>
       </c>
       <c r="G104" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H104" t="str">
         <v>Ok</v>
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="G105" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H105" t="str">
         <v>Ok</v>
@@ -4412,7 +4412,7 @@
         <v/>
       </c>
       <c r="G106" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H106" t="str">
         <v>Ok</v>
@@ -4450,7 +4450,7 @@
         <v/>
       </c>
       <c r="G107" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H107" t="str">
         <v>Ok</v>
@@ -4488,7 +4488,7 @@
         <v/>
       </c>
       <c r="G108" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H108" t="str">
         <v>Ok</v>
@@ -4526,7 +4526,7 @@
         <v/>
       </c>
       <c r="G109" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H109" t="str">
         <v>Ok</v>
@@ -4564,7 +4564,7 @@
         <v/>
       </c>
       <c r="G110" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H110" t="str">
         <v>Ok</v>
@@ -4602,7 +4602,7 @@
         <v/>
       </c>
       <c r="G111" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H111" t="str">
         <v>Ok</v>
@@ -4640,7 +4640,7 @@
         <v/>
       </c>
       <c r="G112" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H112" t="str">
         <v>Ok</v>
@@ -4678,7 +4678,7 @@
         <v/>
       </c>
       <c r="G113" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H113" t="str">
         <v>Ok</v>
@@ -4716,7 +4716,7 @@
         <v/>
       </c>
       <c r="G114" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H114" t="str">
         <v>Ok</v>
@@ -4754,7 +4754,7 @@
         <v/>
       </c>
       <c r="G115" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H115" t="str">
         <v>Ok</v>
@@ -4792,7 +4792,7 @@
         <v/>
       </c>
       <c r="G116" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H116" t="str">
         <v>Ok</v>
@@ -4830,7 +4830,7 @@
         <v/>
       </c>
       <c r="G117" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H117" t="str">
         <v>Ok</v>
@@ -4868,7 +4868,7 @@
         <v/>
       </c>
       <c r="G118" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H118" t="str">
         <v>Ok</v>
@@ -4982,7 +4982,7 @@
         <v/>
       </c>
       <c r="G121" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H121" t="str">
         <v>Ok</v>
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="G122" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H122" t="str">
         <v>Ok</v>
@@ -5058,7 +5058,7 @@
         <v/>
       </c>
       <c r="G123" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H123" t="str">
         <v>Ok</v>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="G124" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H124" t="str">
         <v>Ok</v>
@@ -5134,7 +5134,7 @@
         <v/>
       </c>
       <c r="G125" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H125" t="str">
         <v>Ok</v>
@@ -5172,7 +5172,7 @@
         <v/>
       </c>
       <c r="G126" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H126" t="str">
         <v>Ok</v>
@@ -5210,7 +5210,7 @@
         <v/>
       </c>
       <c r="G127" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H127" t="str">
         <v>Ok</v>
@@ -5248,7 +5248,7 @@
         <v/>
       </c>
       <c r="G128" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H128" t="str">
         <v>Ok</v>
@@ -5286,7 +5286,7 @@
         <v/>
       </c>
       <c r="G129" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H129" t="str">
         <v>Ok</v>
@@ -5324,7 +5324,7 @@
         <v/>
       </c>
       <c r="G130" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H130" t="str">
         <v>Ok</v>
@@ -5362,7 +5362,7 @@
         <v/>
       </c>
       <c r="G131" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H131" t="str">
         <v>Ok</v>
@@ -5400,7 +5400,7 @@
         <v/>
       </c>
       <c r="G132" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H132" t="str">
         <v>Ok</v>
@@ -5438,7 +5438,7 @@
         <v/>
       </c>
       <c r="G133" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H133" t="str">
         <v>Ok</v>
@@ -5476,7 +5476,7 @@
         <v/>
       </c>
       <c r="G134" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H134" t="str">
         <v>Ok</v>
@@ -5514,7 +5514,7 @@
         <v/>
       </c>
       <c r="G135" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H135" t="str">
         <v>Ok</v>
@@ -5552,7 +5552,7 @@
         <v/>
       </c>
       <c r="G136" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H136" t="str">
         <v>Ok</v>
@@ -5590,7 +5590,7 @@
         <v/>
       </c>
       <c r="G137" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H137" t="str">
         <v>Ok</v>
@@ -5628,7 +5628,7 @@
         <v/>
       </c>
       <c r="G138" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H138" t="str">
         <v>Ok</v>
@@ -5666,7 +5666,7 @@
         <v/>
       </c>
       <c r="G139" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H139" t="str">
         <v>Ok</v>
@@ -5704,7 +5704,7 @@
         <v/>
       </c>
       <c r="G140" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H140" t="str">
         <v>Ok</v>
@@ -5742,7 +5742,7 @@
         <v/>
       </c>
       <c r="G141" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H141" t="str">
         <v>Ok</v>
@@ -5780,7 +5780,7 @@
         <v/>
       </c>
       <c r="G142" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H142" t="str">
         <v>Ok</v>
@@ -5818,7 +5818,7 @@
         <v/>
       </c>
       <c r="G143" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H143" t="str">
         <v>Ok</v>
@@ -5970,7 +5970,7 @@
         <v/>
       </c>
       <c r="G147" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H147" t="str">
         <v>Ok</v>
@@ -6008,7 +6008,7 @@
         <v/>
       </c>
       <c r="G148" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H148" t="str">
         <v>Ok</v>
@@ -6046,7 +6046,7 @@
         <v/>
       </c>
       <c r="G149" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H149" t="str">
         <v>Ok</v>
@@ -6084,7 +6084,7 @@
         <v/>
       </c>
       <c r="G150" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H150" t="str">
         <v>Ok</v>
@@ -6502,7 +6502,7 @@
         <v/>
       </c>
       <c r="G161" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H161" t="str">
         <v>Ok</v>
@@ -6540,7 +6540,7 @@
         <v/>
       </c>
       <c r="G162" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H162" t="str">
         <v>Ok</v>
@@ -6578,7 +6578,7 @@
         <v/>
       </c>
       <c r="G163" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H163" t="str">
         <v>Ok</v>
@@ -6616,7 +6616,7 @@
         <v/>
       </c>
       <c r="G164" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H164" t="str">
         <v>NONONO</v>
@@ -6654,7 +6654,7 @@
         <v/>
       </c>
       <c r="G165" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H165" t="str">
         <v>Ok</v>
@@ -6692,7 +6692,7 @@
         <v/>
       </c>
       <c r="G166" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H166" t="str">
         <v>NONONO</v>
@@ -6730,7 +6730,7 @@
         <v/>
       </c>
       <c r="G167" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H167" t="str">
         <v>NONONO</v>
@@ -6768,7 +6768,7 @@
         <v/>
       </c>
       <c r="G168" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H168" t="str">
         <v>NONONO</v>
@@ -6806,7 +6806,7 @@
         <v/>
       </c>
       <c r="G169" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H169" t="str">
         <v>Ok</v>
@@ -6844,7 +6844,7 @@
         <v/>
       </c>
       <c r="G170" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H170" t="str">
         <v>NONONO</v>
@@ -6882,7 +6882,7 @@
         <v/>
       </c>
       <c r="G171" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H171" t="str">
         <v>Ok</v>
@@ -6920,7 +6920,7 @@
         <v/>
       </c>
       <c r="G172" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H172" t="str">
         <v>NONONO</v>
@@ -6958,7 +6958,7 @@
         <v/>
       </c>
       <c r="G173" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H173" t="str">
         <v>Ok</v>
@@ -6996,7 +6996,7 @@
         <v/>
       </c>
       <c r="G174" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H174" t="str">
         <v>Ok</v>
@@ -7034,7 +7034,7 @@
         <v/>
       </c>
       <c r="G175" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H175" t="str">
         <v>Ok</v>
@@ -7072,7 +7072,7 @@
         <v/>
       </c>
       <c r="G176" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H176" t="str">
         <v>Ok</v>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="G177" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H177" t="str">
         <v>Ok</v>
@@ -7148,7 +7148,7 @@
         <v/>
       </c>
       <c r="G178" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H178" t="str">
         <v>Ok</v>
@@ -7186,7 +7186,7 @@
         <v/>
       </c>
       <c r="G179" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H179" t="str">
         <v>Ok</v>
@@ -7224,7 +7224,7 @@
         <v/>
       </c>
       <c r="G180" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H180" t="str">
         <v>Ok</v>
@@ -7262,7 +7262,7 @@
         <v/>
       </c>
       <c r="G181" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H181" t="str">
         <v>Ok</v>
@@ -7300,7 +7300,7 @@
         <v/>
       </c>
       <c r="G182" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H182" t="str">
         <v>NONONO</v>
@@ -7338,7 +7338,7 @@
         <v/>
       </c>
       <c r="G183" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H183" t="str">
         <v>Ok</v>
@@ -7376,7 +7376,7 @@
         <v/>
       </c>
       <c r="G184" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H184" t="str">
         <v>Ok</v>
@@ -7414,7 +7414,7 @@
         <v/>
       </c>
       <c r="G185" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H185" t="str">
         <v>Ok</v>
@@ -7452,7 +7452,7 @@
         <v/>
       </c>
       <c r="G186" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H186" t="str">
         <v>Ok</v>
@@ -7490,7 +7490,7 @@
         <v/>
       </c>
       <c r="G187" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H187" t="str">
         <v>Ok</v>
@@ -7528,7 +7528,7 @@
         <v/>
       </c>
       <c r="G188" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H188" t="str">
         <v>Ok</v>
@@ -7566,7 +7566,7 @@
         <v/>
       </c>
       <c r="G189" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H189" t="str">
         <v>Ok</v>
@@ -7604,7 +7604,7 @@
         <v/>
       </c>
       <c r="G190" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H190" t="str">
         <v>NONONO</v>
@@ -7642,7 +7642,7 @@
         <v/>
       </c>
       <c r="G191" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H191" t="str">
         <v>NONONO</v>
@@ -7680,7 +7680,7 @@
         <v/>
       </c>
       <c r="G192" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H192" t="str">
         <v>NONONO</v>
@@ -7718,7 +7718,7 @@
         <v/>
       </c>
       <c r="G193" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H193" t="str">
         <v>Ok</v>
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="G194" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H194" t="str">
         <v>NONONO</v>
@@ -7794,7 +7794,7 @@
         <v/>
       </c>
       <c r="G195" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H195" t="str">
         <v>NONONO</v>
@@ -7832,7 +7832,7 @@
         <v/>
       </c>
       <c r="G196" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H196" t="str">
         <v>NONONO</v>
@@ -7870,7 +7870,7 @@
         <v/>
       </c>
       <c r="G197" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H197" t="str">
         <v>NONONO</v>
@@ -7908,7 +7908,7 @@
         <v/>
       </c>
       <c r="G198" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H198" t="str">
         <v>NONONO</v>
@@ -7946,7 +7946,7 @@
         <v/>
       </c>
       <c r="G199" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H199" t="str">
         <v>NONONO</v>
@@ -7984,7 +7984,7 @@
         <v/>
       </c>
       <c r="G200" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H200" t="str">
         <v>NONONO</v>
@@ -8022,7 +8022,7 @@
         <v/>
       </c>
       <c r="G201" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H201" t="str">
         <v>Ok</v>
@@ -8060,7 +8060,7 @@
         <v/>
       </c>
       <c r="G202" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H202" t="str">
         <v>Ok</v>
@@ -8098,7 +8098,7 @@
         <v/>
       </c>
       <c r="G203" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H203" t="str">
         <v>Ok</v>
@@ -8136,7 +8136,7 @@
         <v/>
       </c>
       <c r="G204" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H204" t="str">
         <v>Ok</v>
@@ -8174,7 +8174,7 @@
         <v/>
       </c>
       <c r="G205" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H205" t="str">
         <v>Ok</v>
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="G206" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H206" t="str">
         <v>Ok</v>
@@ -8250,7 +8250,7 @@
         <v/>
       </c>
       <c r="G207" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H207" t="str">
         <v>NONONO</v>
@@ -8288,7 +8288,7 @@
         <v/>
       </c>
       <c r="G208" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H208" t="str">
         <v>Ok</v>
@@ -8326,7 +8326,7 @@
         <v/>
       </c>
       <c r="G209" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H209" t="str">
         <v>Ok</v>
@@ -8364,7 +8364,7 @@
         <v/>
       </c>
       <c r="G210" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H210" t="str">
         <v>Ok</v>
@@ -8402,7 +8402,7 @@
         <v/>
       </c>
       <c r="G211" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H211" t="str">
         <v>Ok</v>
@@ -8440,7 +8440,7 @@
         <v/>
       </c>
       <c r="G212" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H212" t="str">
         <v>Ok</v>
@@ -8478,7 +8478,7 @@
         <v/>
       </c>
       <c r="G213" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H213" t="str">
         <v>Ok</v>
@@ -8516,7 +8516,7 @@
         <v/>
       </c>
       <c r="G214" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H214" t="str">
         <v>Ok</v>
@@ -8554,7 +8554,7 @@
         <v/>
       </c>
       <c r="G215" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H215" t="str">
         <v>Ok</v>
@@ -8592,7 +8592,7 @@
         <v/>
       </c>
       <c r="G216" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H216" t="str">
         <v>Ok</v>
@@ -8630,7 +8630,7 @@
         <v/>
       </c>
       <c r="G217" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H217" t="str">
         <v>Ok</v>
@@ -8668,7 +8668,7 @@
         <v/>
       </c>
       <c r="G218" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H218" t="str">
         <v>Ok</v>
@@ -8706,7 +8706,7 @@
         <v/>
       </c>
       <c r="G219" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H219" t="str">
         <v>Ok</v>
@@ -8744,7 +8744,7 @@
         <v/>
       </c>
       <c r="G220" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H220" t="str">
         <v>NONONO</v>
@@ -8782,7 +8782,7 @@
         <v/>
       </c>
       <c r="G221" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H221" t="str">
         <v>Ok</v>
@@ -8820,7 +8820,7 @@
         <v/>
       </c>
       <c r="G222" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H222" t="str">
         <v>Ok</v>
@@ -8858,7 +8858,7 @@
         <v/>
       </c>
       <c r="G223" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H223" t="str">
         <v>NONONO</v>
@@ -8896,7 +8896,7 @@
         <v/>
       </c>
       <c r="G224" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H224" t="str">
         <v>Ok</v>
@@ -8934,7 +8934,7 @@
         <v/>
       </c>
       <c r="G225" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H225" t="str">
         <v>NONONO</v>
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="G226" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H226" t="str">
         <v>Ok</v>
@@ -9010,7 +9010,7 @@
         <v/>
       </c>
       <c r="G227" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H227" t="str">
         <v>Ok</v>
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="G228" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H228" t="str">
         <v>Ok</v>
@@ -9086,7 +9086,7 @@
         <v/>
       </c>
       <c r="G229" t="str">
-        <v>Legacy</v>
+        <v/>
       </c>
       <c r="H229" t="str">
         <v>Ok</v>

--- a/7_Alola_Data.xlsx
+++ b/7_Alola_Data.xlsx
@@ -1080,7 +1080,7 @@
         <v>7-12</v>
       </c>
       <c r="G15" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H15" s="1">
         <v>0.16670000000000001</v>
@@ -1127,7 +1127,7 @@
         <v>7-12</v>
       </c>
       <c r="G16" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H16" s="1">
         <v>0.16670000000000001</v>
@@ -1174,7 +1174,7 @@
         <v>7-12</v>
       </c>
       <c r="G17" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H17" s="1">
         <v>0.16670000000000001</v>
@@ -1221,7 +1221,7 @@
         <v>7-12</v>
       </c>
       <c r="G18" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H18" s="1">
         <v>0.16670000000000001</v>
@@ -1268,7 +1268,7 @@
         <v>7-12</v>
       </c>
       <c r="G19" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H19" s="1">
         <v>0.16670000000000001</v>
@@ -1315,7 +1315,7 @@
         <v>7-12</v>
       </c>
       <c r="G20" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H20" s="1">
         <v>0.16670000000000001</v>
@@ -1362,7 +1362,7 @@
         <v>7-12</v>
       </c>
       <c r="G21" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H21" s="1">
         <v>0.1</v>
@@ -1456,7 +1456,7 @@
         <v>10-15</v>
       </c>
       <c r="G23" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H23" s="1">
         <v>0.25</v>
@@ -1503,7 +1503,7 @@
         <v>10-15</v>
       </c>
       <c r="G24" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H24" s="1">
         <v>0.25</v>
@@ -1550,7 +1550,7 @@
         <v>10-15</v>
       </c>
       <c r="G25" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H25" s="1">
         <v>0.25</v>
@@ -1597,7 +1597,7 @@
         <v>10-15</v>
       </c>
       <c r="G26" t="str">
-        <v>6-8</v>
+        <v>5-7</v>
       </c>
       <c r="H26" s="1">
         <v>0.25</v>
@@ -1644,7 +1644,7 @@
         <v>14-19</v>
       </c>
       <c r="G27" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H27" s="1">
         <v>0.2</v>
@@ -1691,7 +1691,7 @@
         <v>14-19</v>
       </c>
       <c r="G28" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H28" s="1">
         <v>0.2</v>
@@ -1738,7 +1738,7 @@
         <v>14-19</v>
       </c>
       <c r="G29" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H29" s="1">
         <v>0.2</v>
@@ -1785,7 +1785,7 @@
         <v>14-19</v>
       </c>
       <c r="G30" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H30" s="1">
         <v>0.2</v>
@@ -1832,7 +1832,7 @@
         <v>14-19</v>
       </c>
       <c r="G31" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H31" s="1">
         <v>0.2</v>
@@ -1879,7 +1879,7 @@
         <v>14-19</v>
       </c>
       <c r="G32" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H32" s="1">
         <v>0.1</v>
@@ -1926,7 +1926,7 @@
         <v>16-21</v>
       </c>
       <c r="G33" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H33" s="1">
         <v>0.3333</v>
@@ -1973,7 +1973,7 @@
         <v>16-21</v>
       </c>
       <c r="G34" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H34" s="1">
         <v>0.3333</v>
@@ -2020,7 +2020,7 @@
         <v>16-21</v>
       </c>
       <c r="G35" t="str">
-        <v>8-10</v>
+        <v>7-9</v>
       </c>
       <c r="H35" s="1">
         <v>0.3333</v>
@@ -2114,7 +2114,7 @@
         <v>20-25</v>
       </c>
       <c r="G37" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H37" s="1">
         <v>0.25</v>
@@ -2161,7 +2161,7 @@
         <v>20-25</v>
       </c>
       <c r="G38" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H38" s="1">
         <v>0.25</v>
@@ -2208,7 +2208,7 @@
         <v>20-25</v>
       </c>
       <c r="G39" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H39" s="1">
         <v>0.25</v>
@@ -2255,7 +2255,7 @@
         <v>20-25</v>
       </c>
       <c r="G40" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H40" s="1">
         <v>0.25</v>
@@ -2349,7 +2349,7 @@
         <v>23-28</v>
       </c>
       <c r="G42" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H42" s="1">
         <v>0.3333</v>
@@ -2396,7 +2396,7 @@
         <v>23-28</v>
       </c>
       <c r="G43" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H43" s="1">
         <v>0.3333</v>
@@ -2443,7 +2443,7 @@
         <v>23-28</v>
       </c>
       <c r="G44" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H44" s="1">
         <v>0.3333</v>
@@ -2490,13 +2490,13 @@
         <v>23-28</v>
       </c>
       <c r="G45" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H45" s="1">
         <v>0.1</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="I45" s="1">
+        <v>0.25</v>
       </c>
       <c r="J45" t="str">
         <v>Legacy</v>
@@ -2584,7 +2584,7 @@
         <v>28-33</v>
       </c>
       <c r="G47" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H47" s="1">
         <v>0.3333</v>
@@ -2631,7 +2631,7 @@
         <v>28-33</v>
       </c>
       <c r="G48" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H48" s="1">
         <v>0.3333</v>
@@ -2678,7 +2678,7 @@
         <v>28-33</v>
       </c>
       <c r="G49" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H49" s="1">
         <v>0.3333</v>
@@ -2772,7 +2772,7 @@
         <v>31-36</v>
       </c>
       <c r="G51" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H51" s="1">
         <v>0.2</v>
@@ -2819,7 +2819,7 @@
         <v>31-36</v>
       </c>
       <c r="G52" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H52" s="1">
         <v>0.2</v>
@@ -2866,7 +2866,7 @@
         <v>31-36</v>
       </c>
       <c r="G53" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H53" s="1">
         <v>0.2</v>
@@ -2913,7 +2913,7 @@
         <v>31-36</v>
       </c>
       <c r="G54" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H54" s="1">
         <v>0.2</v>
@@ -2960,7 +2960,7 @@
         <v>31-36</v>
       </c>
       <c r="G55" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H55" s="1">
         <v>0.2</v>
@@ -3007,7 +3007,7 @@
         <v>31-36</v>
       </c>
       <c r="G56" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H56" s="1">
         <v>0.1</v>
@@ -3054,7 +3054,7 @@
         <v>32-37</v>
       </c>
       <c r="G57" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H57" s="1">
         <v>0.2</v>
@@ -3101,7 +3101,7 @@
         <v>32-37</v>
       </c>
       <c r="G58" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H58" s="1">
         <v>0.2</v>
@@ -3148,7 +3148,7 @@
         <v>32-37</v>
       </c>
       <c r="G59" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H59" s="1">
         <v>0.2</v>
@@ -3195,7 +3195,7 @@
         <v>32-37</v>
       </c>
       <c r="G60" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H60" s="1">
         <v>0.2</v>
@@ -3242,7 +3242,7 @@
         <v>32-37</v>
       </c>
       <c r="G61" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H61" s="1">
         <v>0.2</v>
@@ -3289,7 +3289,7 @@
         <v>32-37</v>
       </c>
       <c r="G62" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H62" s="1">
         <v>0.2</v>
@@ -3336,7 +3336,7 @@
         <v>32-37</v>
       </c>
       <c r="G63" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H63" s="1">
         <v>0.2</v>
@@ -3383,7 +3383,7 @@
         <v>32-37</v>
       </c>
       <c r="G64" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H64" s="1">
         <v>0.2</v>
@@ -3430,7 +3430,7 @@
         <v>32-37</v>
       </c>
       <c r="G65" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H65" s="1">
         <v>0.2</v>
@@ -3477,7 +3477,7 @@
         <v>32-37</v>
       </c>
       <c r="G66" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H66" s="1">
         <v>0.2</v>
@@ -3524,7 +3524,7 @@
         <v>34-39</v>
       </c>
       <c r="G67" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H67" s="1">
         <v>0.16670000000000001</v>
@@ -3571,7 +3571,7 @@
         <v>34-39</v>
       </c>
       <c r="G68" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H68" s="1">
         <v>0.16670000000000001</v>
@@ -3618,7 +3618,7 @@
         <v>34-39</v>
       </c>
       <c r="G69" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H69" s="1">
         <v>0.16670000000000001</v>
@@ -3665,7 +3665,7 @@
         <v>34-39</v>
       </c>
       <c r="G70" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H70" s="1">
         <v>0.16670000000000001</v>
@@ -3712,7 +3712,7 @@
         <v>34-39</v>
       </c>
       <c r="G71" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H71" s="1">
         <v>0.16670000000000001</v>
@@ -3759,7 +3759,7 @@
         <v>34-39</v>
       </c>
       <c r="G72" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H72" s="1">
         <v>0.16670000000000001</v>
@@ -3806,7 +3806,7 @@
         <v>34-39</v>
       </c>
       <c r="G73" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H73" s="1">
         <v>0.1</v>
@@ -3853,7 +3853,7 @@
         <v>35-40</v>
       </c>
       <c r="G74" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H74" s="1">
         <v>0.2</v>
@@ -3900,7 +3900,7 @@
         <v>35-40</v>
       </c>
       <c r="G75" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H75" s="1">
         <v>0.2</v>
@@ -3947,7 +3947,7 @@
         <v>35-40</v>
       </c>
       <c r="G76" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H76" s="1">
         <v>0.2</v>
@@ -3994,7 +3994,7 @@
         <v>35-40</v>
       </c>
       <c r="G77" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H77" s="1">
         <v>0.2</v>
@@ -4041,7 +4041,7 @@
         <v>35-40</v>
       </c>
       <c r="G78" t="str">
-        <v>30-34</v>
+        <v>29-32</v>
       </c>
       <c r="H78" s="1">
         <v>0.2</v>
@@ -4135,7 +4135,7 @@
         <v>38-43</v>
       </c>
       <c r="G80" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H80" s="1">
         <v>0.25</v>
@@ -4182,7 +4182,7 @@
         <v>38-43</v>
       </c>
       <c r="G81" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H81" s="1">
         <v>0.25</v>
@@ -4229,7 +4229,7 @@
         <v>38-43</v>
       </c>
       <c r="G82" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H82" s="1">
         <v>0.25</v>
@@ -4276,7 +4276,7 @@
         <v>38-43</v>
       </c>
       <c r="G83" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H83" s="1">
         <v>0.25</v>
@@ -4323,7 +4323,7 @@
         <v>43-48</v>
       </c>
       <c r="G84" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H84" s="1">
         <v>0.125</v>
@@ -4370,7 +4370,7 @@
         <v>43-48</v>
       </c>
       <c r="G85" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H85" s="1">
         <v>0.125</v>
@@ -4417,7 +4417,7 @@
         <v>43-48</v>
       </c>
       <c r="G86" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H86" s="1">
         <v>0.125</v>
@@ -4464,7 +4464,7 @@
         <v>43-48</v>
       </c>
       <c r="G87" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H87" s="1">
         <v>0.125</v>
@@ -4511,7 +4511,7 @@
         <v>43-48</v>
       </c>
       <c r="G88" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H88" s="1">
         <v>0.125</v>
@@ -4558,7 +4558,7 @@
         <v>43-48</v>
       </c>
       <c r="G89" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H89" s="1">
         <v>0.125</v>
@@ -4605,7 +4605,7 @@
         <v>43-48</v>
       </c>
       <c r="G90" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H90" s="1">
         <v>0.125</v>
@@ -4652,7 +4652,7 @@
         <v>43-48</v>
       </c>
       <c r="G91" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H91" s="1">
         <v>0.125</v>
@@ -4746,7 +4746,7 @@
         <v>48-53</v>
       </c>
       <c r="G93" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H93" s="1">
         <v>0.2</v>
@@ -4793,7 +4793,7 @@
         <v>48-53</v>
       </c>
       <c r="G94" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H94" s="1">
         <v>0.2</v>
@@ -4840,7 +4840,7 @@
         <v>48-53</v>
       </c>
       <c r="G95" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H95" s="1">
         <v>0.2</v>
@@ -4887,7 +4887,7 @@
         <v>48-53</v>
       </c>
       <c r="G96" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H96" s="1">
         <v>0.2</v>
@@ -4934,7 +4934,7 @@
         <v>48-53</v>
       </c>
       <c r="G97" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H97" s="1">
         <v>0.2</v>
@@ -4981,7 +4981,7 @@
         <v>52-57</v>
       </c>
       <c r="G98" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H98" s="1">
         <v>0.25</v>
@@ -5028,7 +5028,7 @@
         <v>52-57</v>
       </c>
       <c r="G99" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H99" s="1">
         <v>0.25</v>
@@ -5075,7 +5075,7 @@
         <v>52-57</v>
       </c>
       <c r="G100" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H100" s="1">
         <v>0.25</v>
@@ -5122,7 +5122,7 @@
         <v>52-57</v>
       </c>
       <c r="G101" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H101" s="1">
         <v>0.25</v>
@@ -5216,7 +5216,7 @@
         <v>58-63</v>
       </c>
       <c r="G103" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H103" s="1">
         <v>0.2</v>
@@ -5263,7 +5263,7 @@
         <v>58-63</v>
       </c>
       <c r="G104" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H104" s="1">
         <v>0.2</v>
@@ -5310,7 +5310,7 @@
         <v>58-63</v>
       </c>
       <c r="G105" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H105" s="1">
         <v>0.2</v>
@@ -5357,7 +5357,7 @@
         <v>58-63</v>
       </c>
       <c r="G106" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H106" s="1">
         <v>0.2</v>
@@ -5404,7 +5404,7 @@
         <v>58-63</v>
       </c>
       <c r="G107" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H107" s="1">
         <v>0.2</v>
@@ -5451,7 +5451,7 @@
         <v>60-65</v>
       </c>
       <c r="G108" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H108" s="1">
         <v>0.16670000000000001</v>
@@ -5498,7 +5498,7 @@
         <v>60-65</v>
       </c>
       <c r="G109" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H109" s="1">
         <v>0.16670000000000001</v>
@@ -5545,7 +5545,7 @@
         <v>60-65</v>
       </c>
       <c r="G110" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H110" s="1">
         <v>0.16670000000000001</v>
@@ -5592,7 +5592,7 @@
         <v>60-65</v>
       </c>
       <c r="G111" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H111" s="1">
         <v>0.16670000000000001</v>
@@ -5639,7 +5639,7 @@
         <v>60-65</v>
       </c>
       <c r="G112" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H112" s="1">
         <v>0.16670000000000001</v>
@@ -5686,7 +5686,7 @@
         <v>60-65</v>
       </c>
       <c r="G113" t="str">
-        <v>42-47</v>
+        <v>42-46</v>
       </c>
       <c r="H113" s="1">
         <v>0.16670000000000001</v>
@@ -5733,7 +5733,7 @@
         <v>63-68</v>
       </c>
       <c r="G114" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H114" s="1">
         <v>0.25</v>
@@ -5780,7 +5780,7 @@
         <v>63-68</v>
       </c>
       <c r="G115" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H115" s="1">
         <v>0.25</v>
@@ -5827,7 +5827,7 @@
         <v>63-68</v>
       </c>
       <c r="G116" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H116" s="1">
         <v>0.25</v>
@@ -5874,7 +5874,7 @@
         <v>63-68</v>
       </c>
       <c r="G117" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H117" s="1">
         <v>0.25</v>
@@ -5921,13 +5921,13 @@
         <v>63-68</v>
       </c>
       <c r="G118" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H118" s="1">
         <v>0.1</v>
       </c>
-      <c r="I118" t="str">
-        <v/>
+      <c r="I118" s="1">
+        <v>0.2</v>
       </c>
       <c r="J118" t="str">
         <v>Legacy</v>
@@ -6062,7 +6062,7 @@
         <v>69-74</v>
       </c>
       <c r="G121" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H121" s="1">
         <v>0.3333</v>
@@ -6109,7 +6109,7 @@
         <v>69-74</v>
       </c>
       <c r="G122" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H122" s="1">
         <v>0.3333</v>
@@ -6156,7 +6156,7 @@
         <v>69-74</v>
       </c>
       <c r="G123" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H123" s="1">
         <v>0.3333</v>
@@ -6203,7 +6203,7 @@
         <v>70-75</v>
       </c>
       <c r="G124" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H124" s="1">
         <v>0.2</v>
@@ -6250,7 +6250,7 @@
         <v>70-75</v>
       </c>
       <c r="G125" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H125" s="1">
         <v>0.2</v>
@@ -6297,7 +6297,7 @@
         <v>70-75</v>
       </c>
       <c r="G126" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H126" s="1">
         <v>0.2</v>
@@ -6344,7 +6344,7 @@
         <v>70-75</v>
       </c>
       <c r="G127" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H127" s="1">
         <v>0.2</v>
@@ -6391,7 +6391,7 @@
         <v>70-75</v>
       </c>
       <c r="G128" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H128" s="1">
         <v>0.2</v>
@@ -6438,7 +6438,7 @@
         <v>72-77</v>
       </c>
       <c r="G129" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H129" s="1">
         <v>0.2</v>
@@ -6485,7 +6485,7 @@
         <v>72-77</v>
       </c>
       <c r="G130" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H130" s="1">
         <v>0.2</v>
@@ -6532,7 +6532,7 @@
         <v>72-77</v>
       </c>
       <c r="G131" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H131" s="1">
         <v>0.2</v>
@@ -6579,7 +6579,7 @@
         <v>72-77</v>
       </c>
       <c r="G132" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6626,7 +6626,7 @@
         <v>72-77</v>
       </c>
       <c r="G133" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H133" s="1">
         <v>0.2</v>
@@ -6673,7 +6673,7 @@
         <v>73-78</v>
       </c>
       <c r="G134" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H134" s="1">
         <v>0.16670000000000001</v>
@@ -6720,7 +6720,7 @@
         <v>73-78</v>
       </c>
       <c r="G135" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H135" s="1">
         <v>0.16670000000000001</v>
@@ -6767,7 +6767,7 @@
         <v>73-78</v>
       </c>
       <c r="G136" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H136" s="1">
         <v>0.16670000000000001</v>
@@ -6814,7 +6814,7 @@
         <v>73-78</v>
       </c>
       <c r="G137" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H137" s="1">
         <v>0.16670000000000001</v>
@@ -6861,7 +6861,7 @@
         <v>73-78</v>
       </c>
       <c r="G138" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H138" s="1">
         <v>0.16670000000000001</v>
@@ -6908,7 +6908,7 @@
         <v>73-78</v>
       </c>
       <c r="G139" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H139" s="1">
         <v>0.16670000000000001</v>
@@ -6955,7 +6955,7 @@
         <v>75-80</v>
       </c>
       <c r="G140" t="str">
-        <v>54-60</v>
+        <v>54-59</v>
       </c>
       <c r="H140" s="1">
         <v>0.3333</v>
@@ -7002,7 +7002,7 @@
         <v>75-80</v>
       </c>
       <c r="G141" t="str">
-        <v>54-60</v>
+        <v>54-59</v>
       </c>
       <c r="H141" s="1">
         <v>0.3333</v>
@@ -7049,7 +7049,7 @@
         <v>75-80</v>
       </c>
       <c r="G142" t="str">
-        <v>54-60</v>
+        <v>54-59</v>
       </c>
       <c r="H142" s="1">
         <v>0.3333</v>
@@ -7096,13 +7096,13 @@
         <v>75-80</v>
       </c>
       <c r="G143" t="str">
-        <v>54-60</v>
+        <v>54-59</v>
       </c>
       <c r="H143" s="1">
         <v>0.1</v>
       </c>
-      <c r="I143" t="str">
-        <v/>
+      <c r="I143" s="1">
+        <v>0.25</v>
       </c>
       <c r="J143" t="str">
         <v>Yes</v>
@@ -7284,7 +7284,7 @@
         <v>82-87</v>
       </c>
       <c r="G147" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H147" s="1">
         <v>0.25</v>
@@ -7331,7 +7331,7 @@
         <v>82-87</v>
       </c>
       <c r="G148" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H148" s="1">
         <v>0.25</v>
@@ -7378,7 +7378,7 @@
         <v>82-87</v>
       </c>
       <c r="G149" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H149" s="1">
         <v>0.25</v>
@@ -7425,7 +7425,7 @@
         <v>82-87</v>
       </c>
       <c r="G150" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H150" s="1">
         <v>0.25</v>
@@ -7942,7 +7942,7 @@
         <v>85-90</v>
       </c>
       <c r="G161" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H161" s="1">
         <v>0.3333</v>
@@ -7989,7 +7989,7 @@
         <v>85-90</v>
       </c>
       <c r="G162" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H162" s="1">
         <v>0.3333</v>
@@ -8036,7 +8036,7 @@
         <v>85-90</v>
       </c>
       <c r="G163" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H163" s="1">
         <v>0.3333</v>
@@ -8083,7 +8083,7 @@
         <v>85-90</v>
       </c>
       <c r="G164" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H164" s="1">
         <v>0.25</v>
@@ -8130,7 +8130,7 @@
         <v>85-90</v>
       </c>
       <c r="G165" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H165" s="1">
         <v>0.25</v>
@@ -8177,7 +8177,7 @@
         <v>85-90</v>
       </c>
       <c r="G166" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H166" s="1">
         <v>0.25</v>
@@ -8224,7 +8224,7 @@
         <v>85-90</v>
       </c>
       <c r="G167" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H167" s="1">
         <v>0.25</v>
@@ -8271,7 +8271,7 @@
         <v>85-90</v>
       </c>
       <c r="G168" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H168" s="1">
         <v>0.16670000000000001</v>
@@ -8318,7 +8318,7 @@
         <v>85-90</v>
       </c>
       <c r="G169" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H169" s="1">
         <v>0.16670000000000001</v>
@@ -8365,7 +8365,7 @@
         <v>85-90</v>
       </c>
       <c r="G170" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H170" s="1">
         <v>0.16670000000000001</v>
@@ -8412,7 +8412,7 @@
         <v>85-90</v>
       </c>
       <c r="G171" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H171" s="1">
         <v>0.16670000000000001</v>
@@ -8459,7 +8459,7 @@
         <v>85-90</v>
       </c>
       <c r="G172" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H172" s="1">
         <v>0.16670000000000001</v>
@@ -8506,7 +8506,7 @@
         <v>85-90</v>
       </c>
       <c r="G173" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H173" s="1">
         <v>0.16670000000000001</v>
@@ -8553,7 +8553,7 @@
         <v>85-90</v>
       </c>
       <c r="G174" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H174" s="1">
         <v>0.3333</v>
@@ -8600,7 +8600,7 @@
         <v>85-90</v>
       </c>
       <c r="G175" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H175" s="1">
         <v>0.3333</v>
@@ -8647,7 +8647,7 @@
         <v>85-90</v>
       </c>
       <c r="G176" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H176" s="1">
         <v>0.3333</v>
@@ -8694,13 +8694,13 @@
         <v>85-90</v>
       </c>
       <c r="G177" t="str">
-        <v>60-67</v>
+        <v>60-66</v>
       </c>
       <c r="H177" s="1">
         <v>0.1</v>
       </c>
-      <c r="I177" t="str">
-        <v/>
+      <c r="I177" s="1">
+        <v>0.25</v>
       </c>
       <c r="J177" t="str">
         <v>Yes</v>
@@ -8741,7 +8741,7 @@
         <v>85-90</v>
       </c>
       <c r="G178" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H178" s="1">
         <v>0.11109999999999999</v>
@@ -8788,7 +8788,7 @@
         <v>85-90</v>
       </c>
       <c r="G179" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H179" s="1">
         <v>0.11109999999999999</v>
@@ -8835,7 +8835,7 @@
         <v>85-90</v>
       </c>
       <c r="G180" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H180" s="1">
         <v>0.11109999999999999</v>
@@ -8882,7 +8882,7 @@
         <v>85-90</v>
       </c>
       <c r="G181" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H181" s="1">
         <v>0.11109999999999999</v>
@@ -8929,7 +8929,7 @@
         <v>85-90</v>
       </c>
       <c r="G182" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H182" s="1">
         <v>0.11109999999999999</v>
@@ -8976,7 +8976,7 @@
         <v>85-90</v>
       </c>
       <c r="G183" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H183" s="1">
         <v>0.11109999999999999</v>
@@ -9023,7 +9023,7 @@
         <v>85-90</v>
       </c>
       <c r="G184" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H184" s="1">
         <v>0.11109999999999999</v>
@@ -9070,7 +9070,7 @@
         <v>85-90</v>
       </c>
       <c r="G185" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H185" s="1">
         <v>0.11109999999999999</v>
@@ -9117,7 +9117,7 @@
         <v>85-90</v>
       </c>
       <c r="G186" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H186" s="1">
         <v>0.11109999999999999</v>
@@ -9164,7 +9164,7 @@
         <v>95-100</v>
       </c>
       <c r="G187" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H187" s="1">
         <v>0.3333</v>
@@ -9211,7 +9211,7 @@
         <v>95-100</v>
       </c>
       <c r="G188" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H188" s="1">
         <v>0.3333</v>
@@ -9258,7 +9258,7 @@
         <v>95-100</v>
       </c>
       <c r="G189" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H189" s="1">
         <v>0.3333</v>
@@ -9305,7 +9305,7 @@
         <v>85-90</v>
       </c>
       <c r="G190" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H190" s="1">
         <v>0.125</v>
@@ -9352,7 +9352,7 @@
         <v>85-90</v>
       </c>
       <c r="G191" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H191" s="1">
         <v>0.125</v>
@@ -9399,7 +9399,7 @@
         <v>85-90</v>
       </c>
       <c r="G192" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H192" s="1">
         <v>0.125</v>
@@ -9446,7 +9446,7 @@
         <v>85-90</v>
       </c>
       <c r="G193" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H193" s="1">
         <v>0.125</v>
@@ -9493,7 +9493,7 @@
         <v>85-90</v>
       </c>
       <c r="G194" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H194" s="1">
         <v>0.125</v>
@@ -9540,7 +9540,7 @@
         <v>85-90</v>
       </c>
       <c r="G195" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H195" s="1">
         <v>0.125</v>
@@ -9587,7 +9587,7 @@
         <v>85-90</v>
       </c>
       <c r="G196" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H196" s="1">
         <v>0.125</v>
@@ -9634,7 +9634,7 @@
         <v>85-90</v>
       </c>
       <c r="G197" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H197" s="1">
         <v>0.125</v>
@@ -9681,7 +9681,7 @@
         <v>85-90</v>
       </c>
       <c r="G198" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H198" s="1">
         <v>0.3333</v>
@@ -9728,7 +9728,7 @@
         <v>85-90</v>
       </c>
       <c r="G199" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H199" s="1">
         <v>0.3333</v>
@@ -9775,7 +9775,7 @@
         <v>85-90</v>
       </c>
       <c r="G200" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H200" s="1">
         <v>0.3333</v>
@@ -9822,7 +9822,7 @@
         <v>100-100</v>
       </c>
       <c r="G201" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H201" s="1">
         <v>0.25</v>
@@ -9869,7 +9869,7 @@
         <v>100-100</v>
       </c>
       <c r="G202" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H202" s="1">
         <v>0.25</v>
@@ -9916,7 +9916,7 @@
         <v>100-100</v>
       </c>
       <c r="G203" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H203" s="1">
         <v>0.25</v>
@@ -9963,7 +9963,7 @@
         <v>100-100</v>
       </c>
       <c r="G204" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H204" s="1">
         <v>0.25</v>
@@ -10010,7 +10010,7 @@
         <v>85-90</v>
       </c>
       <c r="G205" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H205" s="1">
         <v>0.3333</v>
@@ -10057,7 +10057,7 @@
         <v>85-90</v>
       </c>
       <c r="G206" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H206" s="1">
         <v>0.3333</v>
@@ -10104,7 +10104,7 @@
         <v>85-90</v>
       </c>
       <c r="G207" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H207" s="1">
         <v>0.3333</v>
@@ -10151,7 +10151,7 @@
         <v>110-110</v>
       </c>
       <c r="G208" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H208" s="1">
         <v>0.1</v>
@@ -10198,7 +10198,7 @@
         <v>110-110</v>
       </c>
       <c r="G209" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H209" s="1">
         <v>0.1</v>
@@ -10245,7 +10245,7 @@
         <v>110-110</v>
       </c>
       <c r="G210" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H210" s="1">
         <v>0.1</v>
@@ -10292,7 +10292,7 @@
         <v>110-110</v>
       </c>
       <c r="G211" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H211" s="1">
         <v>0.1</v>
@@ -10339,7 +10339,7 @@
         <v>110-110</v>
       </c>
       <c r="G212" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H212" s="1">
         <v>0.1</v>
@@ -10386,7 +10386,7 @@
         <v>110-110</v>
       </c>
       <c r="G213" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H213" s="1">
         <v>0.1</v>
@@ -10433,7 +10433,7 @@
         <v>110-110</v>
       </c>
       <c r="G214" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H214" s="1">
         <v>0.1</v>
@@ -10480,7 +10480,7 @@
         <v>110-110</v>
       </c>
       <c r="G215" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H215" s="1">
         <v>0.1</v>
@@ -10527,7 +10527,7 @@
         <v>110-110</v>
       </c>
       <c r="G216" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H216" s="1">
         <v>0.1</v>
@@ -10574,7 +10574,7 @@
         <v>110-110</v>
       </c>
       <c r="G217" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H217" s="1">
         <v>0.1</v>
@@ -10621,13 +10621,13 @@
         <v>85-90</v>
       </c>
       <c r="G218" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H218" s="1">
         <v>0.5</v>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J218" t="str">
         <v/>
@@ -10668,13 +10668,13 @@
         <v>85-90</v>
       </c>
       <c r="G219" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H219" s="1">
         <v>0.5</v>
       </c>
-      <c r="I219" t="str">
-        <v/>
+      <c r="I219" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J219" t="str">
         <v/>
@@ -10715,13 +10715,13 @@
         <v>85-90</v>
       </c>
       <c r="G220" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H220" s="1">
         <v>0.1</v>
       </c>
-      <c r="I220" t="str">
-        <v/>
+      <c r="I220" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J220" t="str">
         <v/>
@@ -10762,7 +10762,7 @@
         <v>85-90</v>
       </c>
       <c r="G221" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H221" s="1">
         <v>1</v>
@@ -10809,7 +10809,7 @@
         <v>85-90</v>
       </c>
       <c r="G222" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H222" s="1">
         <v>0.3333</v>
@@ -10856,7 +10856,7 @@
         <v>85-90</v>
       </c>
       <c r="G223" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H223" s="1">
         <v>0.3333</v>
@@ -10903,7 +10903,7 @@
         <v>85-90</v>
       </c>
       <c r="G224" t="str">
-        <v>60-67</v>
+        <v>96-104</v>
       </c>
       <c r="H224" s="1">
         <v>0.3333</v>
@@ -10950,13 +10950,13 @@
         <v>110-110</v>
       </c>
       <c r="G225" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H225" s="1">
         <v>0.6</v>
       </c>
-      <c r="I225" t="str">
-        <v/>
+      <c r="I225" s="1">
+        <v>0.5</v>
       </c>
       <c r="J225" t="str">
         <v>Yes</v>
@@ -10997,13 +10997,13 @@
         <v>110-110</v>
       </c>
       <c r="G226" t="str">
-        <v>60-67</v>
+        <v>110-110</v>
       </c>
       <c r="H226" s="1">
         <v>0.4</v>
       </c>
-      <c r="I226" t="str">
-        <v/>
+      <c r="I226" s="1">
+        <v>0.5</v>
       </c>
       <c r="J226" t="str">
         <v>Yes</v>
@@ -11044,7 +11044,7 @@
         <v>120-120</v>
       </c>
       <c r="G227" t="str">
-        <v>60-67</v>
+        <v>120-120</v>
       </c>
       <c r="H227" s="1">
         <v>0.3333</v>
@@ -11091,7 +11091,7 @@
         <v>120-120</v>
       </c>
       <c r="G228" t="str">
-        <v>60-67</v>
+        <v>120-120</v>
       </c>
       <c r="H228" s="1">
         <v>0.3333</v>
@@ -11138,7 +11138,7 @@
         <v>120-120</v>
       </c>
       <c r="G229" t="str">
-        <v>60-67</v>
+        <v>120-120</v>
       </c>
       <c r="H229" s="1">
         <v>0.3333</v>

--- a/7_Alola_Data.xlsx
+++ b/7_Alola_Data.xlsx
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C3" t="str">
         <v>Route 1 East</v>
@@ -534,10 +534,10 @@
         <v>No</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C4" t="str">
         <v>Route 1 East</v>
@@ -581,10 +581,10 @@
         <v>No</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C5" t="str">
         <v>Route 1 East</v>
@@ -628,10 +628,10 @@
         <v>No</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C6" t="str">
         <v>Route 1 East</v>
@@ -675,10 +675,10 @@
         <v>No</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -689,7 +689,7 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C7" t="str">
         <v>Route 1 East</v>
@@ -722,10 +722,10 @@
         <v>No</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C8" t="str">
         <v>Route 1 East</v>
@@ -769,10 +769,10 @@
         <v>No</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C9" t="str">
         <v>Route 1 East</v>
@@ -816,10 +816,10 @@
         <v>No</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>Route 1 Hau'oli Outskirts</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1 East","count":15}}</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C11" t="str">
         <v>Route 1 Hau'oli Outskirts</v>
@@ -910,10 +910,10 @@
         <v>No</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Route 2 North</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Dark","count":3}}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -921,10 +921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C12" t="str">
         <v>Route 1 Hau'oli Outskirts</v>
@@ -957,10 +957,10 @@
         <v>No</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Route 2 North</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Dark","count":3}}</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -968,10 +968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C13" t="str">
         <v>Route 1 Hau'oli Outskirts</v>
@@ -1004,10 +1004,10 @@
         <v>No</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Route 2 North</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Dark","count":3}}</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C14" t="str">
         <v>Route 1 Hau'oli Outskirts</v>
@@ -1051,10 +1051,10 @@
         <v>No</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Route 2 North</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Dark","count":3}}</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1085,8 +1085,8 @@
       <c r="H15" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
+      <c r="I15" s="1">
+        <v>0.14</v>
       </c>
       <c r="J15" t="str">
         <v>Yes</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C16" t="str">
         <v>Route 2 North</v>
@@ -1132,8 +1132,8 @@
       <c r="H16" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I16" t="str">
-        <v/>
+      <c r="I16" s="1">
+        <v>0.14</v>
       </c>
       <c r="J16" t="str">
         <v>Yes</v>
@@ -1145,10 +1145,10 @@
         <v>No</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C17" t="str">
         <v>Route 2 North</v>
@@ -1179,8 +1179,8 @@
       <c r="H17" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
+      <c r="I17" s="1">
+        <v>0.14</v>
       </c>
       <c r="J17" t="str">
         <v>Yes</v>
@@ -1192,10 +1192,10 @@
         <v>No</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C18" t="str">
         <v>Route 2 North</v>
@@ -1226,8 +1226,8 @@
       <c r="H18" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
+      <c r="I18" s="1">
+        <v>0.14</v>
       </c>
       <c r="J18" t="str">
         <v>Yes</v>
@@ -1239,10 +1239,10 @@
         <v>No</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C19" t="str">
         <v>Route 2 North</v>
@@ -1273,8 +1273,8 @@
       <c r="H19" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
+      <c r="I19" s="1">
+        <v>0.14</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -1286,10 +1286,10 @@
         <v>No</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C20" t="str">
         <v>Route 2 North</v>
@@ -1320,8 +1320,8 @@
       <c r="H20" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20" s="1">
+        <v>0.14</v>
       </c>
       <c r="J20" t="str">
         <v>Yes</v>
@@ -1333,10 +1333,10 @@
         <v>No</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C21" t="str">
         <v>Route 2 North</v>
@@ -1367,8 +1367,8 @@
       <c r="H21" s="1">
         <v>0.1</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
+      <c r="I21" s="1">
+        <v>0.16</v>
       </c>
       <c r="J21" t="str">
         <v>Yes</v>
@@ -1380,10 +1380,10 @@
         <v>No</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Captain Ilima</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C24" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1521,10 +1521,10 @@
         <v>No</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C25" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1568,10 +1568,10 @@
         <v>No</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C26" t="str">
         <v>Hau'oli Cemetery</v>
@@ -1615,10 +1615,10 @@
         <v>No</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>Ten Carat Hill Farthest Hollow</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1649,8 +1649,8 @@
       <c r="H27" s="1">
         <v>0.2</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
+      <c r="I27" s="1">
+        <v>0.17</v>
       </c>
       <c r="J27" t="str">
         <v>Yes</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C28" t="str">
         <v>Ten Carat Hill Farthest Hollow</v>
@@ -1696,8 +1696,8 @@
       <c r="H28" s="1">
         <v>0.2</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
+      <c r="I28" s="1">
+        <v>0.17</v>
       </c>
       <c r="J28" t="str">
         <v>Yes</v>
@@ -1709,10 +1709,10 @@
         <v>No</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>Seaward Cave</v>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C29" t="str">
         <v>Ten Carat Hill Farthest Hollow</v>
@@ -1743,8 +1743,8 @@
       <c r="H29" s="1">
         <v>0.2</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
+      <c r="I29" s="1">
+        <v>0.17</v>
       </c>
       <c r="J29" t="str">
         <v>Yes</v>
@@ -1756,10 +1756,10 @@
         <v>No</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>Seaward Cave</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C30" t="str">
         <v>Ten Carat Hill Farthest Hollow</v>
@@ -1790,8 +1790,8 @@
       <c r="H30" s="1">
         <v>0.2</v>
       </c>
-      <c r="I30" t="str">
-        <v/>
+      <c r="I30" s="1">
+        <v>0.17</v>
       </c>
       <c r="J30" t="str">
         <v>Yes</v>
@@ -1803,10 +1803,10 @@
         <v>No</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>Seaward Cave</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C31" t="str">
         <v>Ten Carat Hill Farthest Hollow</v>
@@ -1837,8 +1837,8 @@
       <c r="H31" s="1">
         <v>0.2</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="I31" s="1">
+        <v>0.17</v>
       </c>
       <c r="J31" t="str">
         <v>Yes</v>
@@ -1850,10 +1850,10 @@
         <v>No</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>Seaward Cave</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C32" t="str">
         <v>Ten Carat Hill Farthest Hollow</v>
@@ -1884,8 +1884,8 @@
       <c r="H32" s="1">
         <v>0.1</v>
       </c>
-      <c r="I32" t="str">
-        <v/>
+      <c r="I32" s="1">
+        <v>0.15</v>
       </c>
       <c r="J32" t="str">
         <v>Yes</v>
@@ -1897,10 +1897,10 @@
         <v>No</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>Seaward Cave</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C38" t="str">
         <v>Paniola Ranch</v>
@@ -2179,10 +2179,10 @@
         <v>No</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Daycare NPC</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Paniola Ranch","count":10}}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C39" t="str">
         <v>Paniola Ranch</v>
@@ -2226,10 +2226,10 @@
         <v>No</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Daycare NPC</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Paniola Ranch","count":10}}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C40" t="str">
         <v>Paniola Ranch</v>
@@ -2273,10 +2273,10 @@
         <v>No</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>Daycare NPC</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Paniola Ranch","count":10}}</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2354,8 +2354,8 @@
       <c r="H42" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
+      <c r="I42" s="1">
+        <v>0.25</v>
       </c>
       <c r="J42" t="str">
         <v>Legacy</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C43" t="str">
         <v>Route 5</v>
@@ -2401,8 +2401,8 @@
       <c r="H43" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
+      <c r="I43" s="1">
+        <v>0.25</v>
       </c>
       <c r="J43" t="str">
         <v>Legacy</v>
@@ -2414,10 +2414,10 @@
         <v>No</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Captain Lana</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C44" t="str">
         <v>Route 5</v>
@@ -2448,8 +2448,8 @@
       <c r="H44" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I44" t="str">
-        <v/>
+      <c r="I44" s="1">
+        <v>0.25</v>
       </c>
       <c r="J44" t="str">
         <v>Legacy</v>
@@ -2461,10 +2461,10 @@
         <v>No</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>Captain Lana</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C45" t="str">
         <v>Route 5</v>
@@ -2508,10 +2508,10 @@
         <v>No</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>Captain Lana</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C48" t="str">
         <v>Wela Volcano Park</v>
@@ -2649,10 +2649,10 @@
         <v>No</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>Captain Kiawe</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Wela Volcano Park","count":15}}</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C49" t="str">
         <v>Wela Volcano Park</v>
@@ -2696,10 +2696,10 @@
         <v>No</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>Captain Kiawe</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Wela Volcano Park","count":15}}</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2777,8 +2777,8 @@
       <c r="H51" s="1">
         <v>0.2</v>
       </c>
-      <c r="I51" t="str">
-        <v/>
+      <c r="I51" s="1">
+        <v>0.17</v>
       </c>
       <c r="J51" t="str">
         <v>Legacy</v>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C52" t="str">
         <v>Route 7</v>
@@ -2824,8 +2824,8 @@
       <c r="H52" s="1">
         <v>0.2</v>
       </c>
-      <c r="I52" t="str">
-        <v/>
+      <c r="I52" s="1">
+        <v>0.17</v>
       </c>
       <c r="J52" t="str">
         <v>Legacy</v>
@@ -2837,10 +2837,10 @@
         <v>No</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":3}}</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C53" t="str">
         <v>Route 7</v>
@@ -2871,8 +2871,8 @@
       <c r="H53" s="1">
         <v>0.2</v>
       </c>
-      <c r="I53" t="str">
-        <v/>
+      <c r="I53" s="1">
+        <v>0.17</v>
       </c>
       <c r="J53" t="str">
         <v>Yes</v>
@@ -2884,10 +2884,10 @@
         <v>No</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":3}}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C54" t="str">
         <v>Route 7</v>
@@ -2918,8 +2918,8 @@
       <c r="H54" s="1">
         <v>0.2</v>
       </c>
-      <c r="I54" t="str">
-        <v/>
+      <c r="I54" s="1">
+        <v>0.17</v>
       </c>
       <c r="J54" t="str">
         <v>Yes</v>
@@ -2931,10 +2931,10 @@
         <v>No</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":3}}</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C55" t="str">
         <v>Route 7</v>
@@ -2965,8 +2965,8 @@
       <c r="H55" s="1">
         <v>0.2</v>
       </c>
-      <c r="I55" t="str">
-        <v/>
+      <c r="I55" s="1">
+        <v>0.17</v>
       </c>
       <c r="J55" t="str">
         <v>Yes</v>
@@ -2978,10 +2978,10 @@
         <v>No</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":3}}</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C56" t="str">
         <v>Route 7</v>
@@ -3012,8 +3012,8 @@
       <c r="H56" s="1">
         <v>0.1</v>
       </c>
-      <c r="I56" t="str">
-        <v/>
+      <c r="I56" s="1">
+        <v>0.15</v>
       </c>
       <c r="J56" t="str">
         <v>Legacy</v>
@@ -3025,10 +3025,10 @@
         <v>No</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Route 8 Fossil Restoration Center Part 1</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":3}}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C58" t="str">
         <v>Route 8 Fossil Restoration Center Part 1</v>
@@ -3119,10 +3119,10 @@
         <v>No</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>Lush Jungle North</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C59" t="str">
         <v>Route 8 Fossil Restoration Center Part 1</v>
@@ -3166,10 +3166,10 @@
         <v>No</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Lush Jungle North</v>
       </c>
       <c r="N59" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C60" t="str">
         <v>Route 8 Fossil Restoration Center Part 1</v>
@@ -3213,10 +3213,10 @@
         <v>No</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>Lush Jungle North</v>
       </c>
       <c r="N60" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C61" t="str">
         <v>Route 8 Fossil Restoration Center Part 1</v>
@@ -3260,10 +3260,10 @@
         <v>No</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Lush Jungle North</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3529,8 +3529,8 @@
       <c r="H67" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I67" t="str">
-        <v/>
+      <c r="I67" s="1">
+        <v>0.14</v>
       </c>
       <c r="J67" t="str">
         <v>Yes</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C68" t="str">
         <v>Lush Jungle North</v>
@@ -3576,8 +3576,8 @@
       <c r="H68" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I68" t="str">
-        <v/>
+      <c r="I68" s="1">
+        <v>0.14</v>
       </c>
       <c r="J68" t="str">
         <v>Yes</v>
@@ -3589,10 +3589,10 @@
         <v>No</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C69" t="str">
         <v>Lush Jungle North</v>
@@ -3623,8 +3623,8 @@
       <c r="H69" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I69" t="str">
-        <v/>
+      <c r="I69" s="1">
+        <v>0.14</v>
       </c>
       <c r="J69" t="str">
         <v>Yes</v>
@@ -3636,10 +3636,10 @@
         <v>No</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C70" t="str">
         <v>Lush Jungle North</v>
@@ -3670,8 +3670,8 @@
       <c r="H70" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
+      <c r="I70" s="1">
+        <v>0.14</v>
       </c>
       <c r="J70" t="str">
         <v>Yes</v>
@@ -3683,10 +3683,10 @@
         <v>No</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C71" t="str">
         <v>Lush Jungle North</v>
@@ -3717,8 +3717,8 @@
       <c r="H71" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I71" t="str">
-        <v/>
+      <c r="I71" s="1">
+        <v>0.14</v>
       </c>
       <c r="J71" t="str">
         <v>Yes</v>
@@ -3730,10 +3730,10 @@
         <v>No</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N71" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C72" t="str">
         <v>Lush Jungle North</v>
@@ -3764,8 +3764,8 @@
       <c r="H72" s="1">
         <v>0.16670000000000001</v>
       </c>
-      <c r="I72" t="str">
-        <v/>
+      <c r="I72" s="1">
+        <v>0.14</v>
       </c>
       <c r="J72" t="str">
         <v>Yes</v>
@@ -3777,10 +3777,10 @@
         <v>No</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C73" t="str">
         <v>Lush Jungle North</v>
@@ -3811,8 +3811,8 @@
       <c r="H73" s="1">
         <v>0.1</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
+      <c r="I73" s="1">
+        <v>0.16</v>
       </c>
       <c r="J73" t="str">
         <v>Yes</v>
@@ -3824,10 +3824,10 @@
         <v>No</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Lush Jungle East Cave</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C75" t="str">
         <v>Lush Jungle East Cave</v>
@@ -3918,10 +3918,10 @@
         <v>No</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Mallow"}</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C76" t="str">
         <v>Lush Jungle East Cave</v>
@@ -3965,10 +3965,10 @@
         <v>No</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="N76" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Mallow"}</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C77" t="str">
         <v>Lush Jungle East Cave</v>
@@ -4012,10 +4012,10 @@
         <v>No</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Mallow"}</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C78" t="str">
         <v>Lush Jungle East Cave</v>
@@ -4059,10 +4059,10 @@
         <v>No</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>Diglett's Tunnel</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Mallow"}</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C81" t="str">
         <v>Diglett's Tunnel</v>
@@ -4200,10 +4200,10 @@
         <v>No</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>Akala Outskirts</v>
       </c>
       <c r="N81" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Diglett's Tunnel","count":10}}</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C82" t="str">
         <v>Diglett's Tunnel</v>
@@ -4247,10 +4247,10 @@
         <v>No</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>Akala Outskirts</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Diglett's Tunnel","count":10}}</v>
       </c>
       <c r="O82" t="str">
         <v/>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C83" t="str">
         <v>Diglett's Tunnel</v>
@@ -4294,10 +4294,10 @@
         <v>No</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Akala Outskirts</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Diglett's Tunnel","count":10}}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C85" t="str">
         <v>Akala Outskirts</v>
@@ -4388,10 +4388,10 @@
         <v>No</v>
       </c>
       <c r="M85" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N85" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C86" t="str">
         <v>Akala Outskirts</v>
@@ -4435,10 +4435,10 @@
         <v>No</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C87" t="str">
         <v>Akala Outskirts</v>
@@ -4482,10 +4482,10 @@
         <v>No</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C88" t="str">
         <v>Akala Outskirts</v>
@@ -4529,10 +4529,10 @@
         <v>No</v>
       </c>
       <c r="M88" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O88" t="str">
         <v/>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C89" t="str">
         <v>Akala Outskirts</v>
@@ -4576,10 +4576,10 @@
         <v>No</v>
       </c>
       <c r="M89" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N89" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O89" t="str">
         <v/>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C90" t="str">
         <v>Akala Outskirts</v>
@@ -4623,10 +4623,10 @@
         <v>No</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C91" t="str">
         <v>Akala Outskirts</v>
@@ -4670,10 +4670,10 @@
         <v>No</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>Malie City</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kahuna Olivia","count":10}}</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C94" t="str">
         <v>Malie City</v>
@@ -4811,10 +4811,10 @@
         <v>No</v>
       </c>
       <c r="M94" t="str">
-        <v/>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Malie City","count":15}}</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B95" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C95" t="str">
         <v>Malie City</v>
@@ -4858,10 +4858,10 @@
         <v>No</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Malie City","count":15}}</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C96" t="str">
         <v>Malie City</v>
@@ -4905,10 +4905,10 @@
         <v>No</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Malie City","count":15}}</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C97" t="str">
         <v>Malie City</v>
@@ -4952,10 +4952,10 @@
         <v>No</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>Mount Hokulani East</v>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Malie City","count":15}}</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C99" t="str">
         <v>Mount Hokulani East</v>
@@ -5046,10 +5046,10 @@
         <v>No</v>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>Haina Desert</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Sophocles","count":10}}</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C100" t="str">
         <v>Mount Hokulani East</v>
@@ -5093,10 +5093,10 @@
         <v>No</v>
       </c>
       <c r="M100" t="str">
-        <v/>
+        <v>Haina Desert</v>
       </c>
       <c r="N100" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Sophocles","count":10}}</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C101" t="str">
         <v>Mount Hokulani East</v>
@@ -5140,10 +5140,10 @@
         <v>No</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Haina Desert</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Sophocles","count":10}}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C104" t="str">
         <v>Haina Desert</v>
@@ -5281,10 +5281,10 @@
         <v>No</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>Tapu Village</v>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C105" t="str">
         <v>Haina Desert</v>
@@ -5328,10 +5328,10 @@
         <v>No</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Tapu Village</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C106" t="str">
         <v>Haina Desert</v>
@@ -5375,10 +5375,10 @@
         <v>No</v>
       </c>
       <c r="M106" t="str">
-        <v/>
+        <v>Tapu Village</v>
       </c>
       <c r="N106" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C107" t="str">
         <v>Haina Desert</v>
@@ -5422,10 +5422,10 @@
         <v>No</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Tapu Village</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C109" t="str">
         <v>Tapu Village</v>
@@ -5516,10 +5516,10 @@
         <v>No</v>
       </c>
       <c r="M109" t="str">
-        <v/>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C110" t="str">
         <v>Tapu Village</v>
@@ -5563,10 +5563,10 @@
         <v>No</v>
       </c>
       <c r="M110" t="str">
-        <v/>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C111" t="str">
         <v>Tapu Village</v>
@@ -5610,10 +5610,10 @@
         <v>No</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C112" t="str">
         <v>Tapu Village</v>
@@ -5657,10 +5657,10 @@
         <v>No</v>
       </c>
       <c r="M112" t="str">
-        <v/>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O112" t="str">
         <v/>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C113" t="str">
         <v>Tapu Village</v>
@@ -5704,10 +5704,10 @@
         <v>No</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Thrifty Megamart</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5738,8 +5738,8 @@
       <c r="H114" s="1">
         <v>0.25</v>
       </c>
-      <c r="I114" t="str">
-        <v/>
+      <c r="I114" s="1">
+        <v>0.2</v>
       </c>
       <c r="J114" t="str">
         <v>Legacy</v>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C115" t="str">
         <v>Thrifty Megamart</v>
@@ -5785,8 +5785,8 @@
       <c r="H115" s="1">
         <v>0.25</v>
       </c>
-      <c r="I115" t="str">
-        <v/>
+      <c r="I115" s="1">
+        <v>0.2</v>
       </c>
       <c r="J115" t="str">
         <v>Legacy</v>
@@ -5798,10 +5798,10 @@
         <v>No</v>
       </c>
       <c r="M115" t="str">
-        <v/>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="N115" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Acerola","count":10}}</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C116" t="str">
         <v>Thrifty Megamart</v>
@@ -5832,8 +5832,8 @@
       <c r="H116" s="1">
         <v>0.25</v>
       </c>
-      <c r="I116" t="str">
-        <v/>
+      <c r="I116" s="1">
+        <v>0.2</v>
       </c>
       <c r="J116" t="str">
         <v>Legacy</v>
@@ -5845,10 +5845,10 @@
         <v>No</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="N116" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Acerola","count":10}}</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C117" t="str">
         <v>Thrifty Megamart</v>
@@ -5879,8 +5879,8 @@
       <c r="H117" s="1">
         <v>0.25</v>
       </c>
-      <c r="I117" t="str">
-        <v/>
+      <c r="I117" s="1">
+        <v>0.2</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -5892,10 +5892,10 @@
         <v>No</v>
       </c>
       <c r="M117" t="str">
-        <v/>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="N117" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Acerola","count":10}}</v>
       </c>
       <c r="O117" t="str">
         <v/>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C118" t="str">
         <v>Thrifty Megamart</v>
@@ -5939,10 +5939,10 @@
         <v>No</v>
       </c>
       <c r="M118" t="str">
-        <v/>
+        <v>Kahuna Nanu</v>
       </c>
       <c r="N118" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Captain Acerola","count":10}}</v>
       </c>
       <c r="O118" t="str">
         <v/>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B122" t="str">
         <v/>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B125" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C125" t="str">
         <v>Poni Wilds</v>
@@ -6268,10 +6268,10 @@
         <v>No</v>
       </c>
       <c r="M125" t="str">
-        <v/>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Poni Wilds","count":10}}</v>
       </c>
       <c r="O125" t="str">
         <v/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C126" t="str">
         <v>Poni Wilds</v>
@@ -6315,10 +6315,10 @@
         <v>No</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="N126" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Poni Wilds","count":10}}</v>
       </c>
       <c r="O126" t="str">
         <v/>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C127" t="str">
         <v>Poni Wilds</v>
@@ -6362,10 +6362,10 @@
         <v>No</v>
       </c>
       <c r="M127" t="str">
-        <v/>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="N127" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Poni Wilds","count":10}}</v>
       </c>
       <c r="O127" t="str">
         <v/>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B128" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C128" t="str">
         <v>Poni Wilds</v>
@@ -6409,10 +6409,10 @@
         <v>No</v>
       </c>
       <c r="M128" t="str">
-        <v/>
+        <v>Poni Breaker Coast</v>
       </c>
       <c r="N128" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Poni Wilds","count":10}}</v>
       </c>
       <c r="O128" t="str">
         <v/>
@@ -6467,10 +6467,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B130" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C130" t="str">
         <v>Poni Breaker Coast</v>
@@ -6503,10 +6503,10 @@
         <v>No</v>
       </c>
       <c r="M130" t="str">
-        <v/>
+        <v>Exeggutor Island</v>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O130" t="str">
         <v/>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C131" t="str">
         <v>Poni Breaker Coast</v>
@@ -6550,10 +6550,10 @@
         <v>No</v>
       </c>
       <c r="M131" t="str">
-        <v/>
+        <v>Exeggutor Island</v>
       </c>
       <c r="N131" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O131" t="str">
         <v/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C132" t="str">
         <v>Poni Breaker Coast</v>
@@ -6597,10 +6597,10 @@
         <v>No</v>
       </c>
       <c r="M132" t="str">
-        <v/>
+        <v>Exeggutor Island</v>
       </c>
       <c r="N132" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O132" t="str">
         <v/>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B133" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C133" t="str">
         <v>Poni Breaker Coast</v>
@@ -6644,10 +6644,10 @@
         <v>No</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>Exeggutor Island</v>
       </c>
       <c r="N133" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O133" t="str">
         <v/>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C135" t="str">
         <v>Exeggutor Island</v>
@@ -6738,10 +6738,10 @@
         <v>No</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Exeggutor Island","count":15}}</v>
       </c>
       <c r="O135" t="str">
         <v/>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B136" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C136" t="str">
         <v>Exeggutor Island</v>
@@ -6785,10 +6785,10 @@
         <v>No</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Exeggutor Island","count":15}}</v>
       </c>
       <c r="O136" t="str">
         <v/>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C137" t="str">
         <v>Exeggutor Island</v>
@@ -6832,10 +6832,10 @@
         <v>No</v>
       </c>
       <c r="M137" t="str">
-        <v/>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="N137" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Exeggutor Island","count":15}}</v>
       </c>
       <c r="O137" t="str">
         <v/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C138" t="str">
         <v>Exeggutor Island</v>
@@ -6879,10 +6879,10 @@
         <v>No</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Exeggutor Island","count":15}}</v>
       </c>
       <c r="O138" t="str">
         <v/>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B139" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C139" t="str">
         <v>Exeggutor Island</v>
@@ -6926,10 +6926,10 @@
         <v>No</v>
       </c>
       <c r="M139" t="str">
-        <v/>
+        <v>Vast Poni Canyon Outside</v>
       </c>
       <c r="N139" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Exeggutor Island","count":15}}</v>
       </c>
       <c r="O139" t="str">
         <v/>
@@ -6960,8 +6960,8 @@
       <c r="H140" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I140" t="str">
-        <v/>
+      <c r="I140" s="1">
+        <v>0.25</v>
       </c>
       <c r="J140" t="str">
         <v>Yes</v>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C141" t="str">
         <v>Vast Poni Canyon Outside</v>
@@ -7007,8 +7007,8 @@
       <c r="H141" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I141" t="str">
-        <v/>
+      <c r="I141" s="1">
+        <v>0.25</v>
       </c>
       <c r="J141" t="str">
         <v>Yes</v>
@@ -7020,10 +7020,10 @@
         <v>No</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Captain Mina</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Kommo-o"}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C142" t="str">
         <v>Vast Poni Canyon Outside</v>
@@ -7054,8 +7054,8 @@
       <c r="H142" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I142" t="str">
-        <v/>
+      <c r="I142" s="1">
+        <v>0.25</v>
       </c>
       <c r="J142" t="str">
         <v>Yes</v>
@@ -7067,10 +7067,10 @@
         <v>No</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Captain Mina</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Kommo-o"}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C143" t="str">
         <v>Vast Poni Canyon Outside</v>
@@ -7114,10 +7114,10 @@
         <v>No</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>Captain Mina</v>
       </c>
       <c r="N143" t="str">
-        <v/>
+        <v>{"defeatBoss":"Captain Kommo-o"}</v>
       </c>
       <c r="O143" t="str">
         <v/>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B148" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C148" t="str">
         <v>Mount Lanakila</v>
@@ -7349,10 +7349,10 @@
         <v>No</v>
       </c>
       <c r="M148" t="str">
-        <v/>
+        <v>Champion Hau</v>
       </c>
       <c r="N148" t="str">
-        <v/>
+        <v>{"defeatAlolaChampion":true}</v>
       </c>
       <c r="O148" t="str">
         <v/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C149" t="str">
         <v>Mount Lanakila</v>
@@ -7396,10 +7396,10 @@
         <v>No</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>Champion Hau</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>{"defeatAlolaChampion":true}</v>
       </c>
       <c r="O149" t="str">
         <v/>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="C150" t="str">
         <v>Mount Lanakila</v>
@@ -7443,10 +7443,10 @@
         <v>No</v>
       </c>
       <c r="M150" t="str">
-        <v/>
+        <v>Champion Hau</v>
       </c>
       <c r="N150" t="str">
-        <v/>
+        <v>{"defeatAlolaChampion":true}</v>
       </c>
       <c r="O150" t="str">
         <v/>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v/>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B162" t="str">
-        <v/>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="C162" t="str">
         <v>Royal Avenue</v>
@@ -8007,10 +8007,10 @@
         <v>No</v>
       </c>
       <c r="M162" t="str">
-        <v/>
+        <v>Pikachu Valley</v>
       </c>
       <c r="N162" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O162" t="str">
         <v/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Extra Challenge A-2</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="C163" t="str">
         <v>Royal Avenue</v>
@@ -8054,10 +8054,10 @@
         <v>No</v>
       </c>
       <c r="M163" t="str">
-        <v/>
+        <v>Pikachu Valley</v>
       </c>
       <c r="N163" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Rare+","count":2}}</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="C165" t="str">
         <v>Pikachu Valley</v>
@@ -8148,10 +8148,10 @@
         <v>No</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Starter Depot</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="C166" t="str">
         <v>Pikachu Valley</v>
@@ -8195,10 +8195,10 @@
         <v>No</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Starter Depot</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v/>
+        <v>Extra Challenge A-3</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="C167" t="str">
         <v>Pikachu Valley</v>
@@ -8242,10 +8242,10 @@
         <v>No</v>
       </c>
       <c r="M167" t="str">
-        <v/>
+        <v>Starter Depot</v>
       </c>
       <c r="N167" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B170" t="str">
         <v/>
@@ -8394,7 +8394,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B172" t="str">
         <v/>
@@ -8488,7 +8488,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v/>
+        <v>Extra Challenge A-4</v>
       </c>
       <c r="B173" t="str">
         <v/>
@@ -8558,8 +8558,8 @@
       <c r="H174" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I174" t="str">
-        <v/>
+      <c r="I174" s="1">
+        <v>0.25</v>
       </c>
       <c r="J174" t="str">
         <v>Legacy</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -8605,8 +8605,8 @@
       <c r="H175" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I175" t="str">
-        <v/>
+      <c r="I175" s="1">
+        <v>0.25</v>
       </c>
       <c r="J175" t="str">
         <v>Legacy</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -8652,8 +8652,8 @@
       <c r="H176" s="1">
         <v>0.3333</v>
       </c>
-      <c r="I176" t="str">
-        <v/>
+      <c r="I176" s="1">
+        <v>0.25</v>
       </c>
       <c r="J176" t="str">
         <v>Legacy</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Extra Challenge B-1</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C179" t="str">
         <v>Blush Mountain</v>
@@ -8806,10 +8806,10 @@
         <v>No</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C180" t="str">
         <v>Blush Mountain</v>
@@ -8853,10 +8853,10 @@
         <v>No</v>
       </c>
       <c r="M180" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N180" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -8864,10 +8864,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C181" t="str">
         <v>Blush Mountain</v>
@@ -8900,10 +8900,10 @@
         <v>No</v>
       </c>
       <c r="M181" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N181" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O181" t="str">
         <v/>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B182" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C182" t="str">
         <v>Blush Mountain</v>
@@ -8947,10 +8947,10 @@
         <v>No</v>
       </c>
       <c r="M182" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N182" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O182" t="str">
         <v/>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C183" t="str">
         <v>Blush Mountain</v>
@@ -8994,10 +8994,10 @@
         <v>No</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C184" t="str">
         <v>Blush Mountain</v>
@@ -9041,10 +9041,10 @@
         <v>No</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9052,10 +9052,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B185" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C185" t="str">
         <v>Blush Mountain</v>
@@ -9088,10 +9088,10 @@
         <v>No</v>
       </c>
       <c r="M185" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N185" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O185" t="str">
         <v/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Extra Challenge B-2</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Extra Challenge B-3</v>
       </c>
       <c r="C186" t="str">
         <v>Blush Mountain</v>
@@ -9135,10 +9135,10 @@
         <v>No</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Shopping Mall Antiquities</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"catchCountRoute":{"route":"Blush Mountain","count":10}}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9193,10 +9193,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v/>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B188" t="str">
-        <v/>
+        <v>Extra Challenge B-5</v>
       </c>
       <c r="C188" t="str">
         <v>The Zenith Anomaly</v>
@@ -9232,7 +9232,7 @@
         <v/>
       </c>
       <c r="N188" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Magearna","count":1},{"species":"Marshadow","count":1},{"species":"Zeraora","count":1}]}</v>
       </c>
       <c r="O188" t="str">
         <v/>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Extra Challenge B-4</v>
       </c>
       <c r="B189" t="str">
-        <v/>
+        <v>Extra Challenge B-5</v>
       </c>
       <c r="C189" t="str">
         <v>The Zenith Anomaly</v>
@@ -9279,7 +9279,7 @@
         <v/>
       </c>
       <c r="N189" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Magearna","count":1},{"species":"Marshadow","count":1},{"species":"Zeraora","count":1}]}</v>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -9337,7 +9337,7 @@
         <v/>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C191" t="str">
         <v>Melemele Meadow</v>
@@ -9370,10 +9370,10 @@
         <v>No</v>
       </c>
       <c r="M191" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N191" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O191" t="str">
         <v/>
@@ -9384,7 +9384,7 @@
         <v/>
       </c>
       <c r="B192" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C192" t="str">
         <v>Melemele Meadow</v>
@@ -9417,10 +9417,10 @@
         <v>No</v>
       </c>
       <c r="M192" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N192" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O192" t="str">
         <v/>
@@ -9431,7 +9431,7 @@
         <v/>
       </c>
       <c r="B193" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C193" t="str">
         <v>Melemele Meadow</v>
@@ -9464,10 +9464,10 @@
         <v>No</v>
       </c>
       <c r="M193" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N193" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -9478,7 +9478,7 @@
         <v/>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C194" t="str">
         <v>Melemele Meadow</v>
@@ -9511,10 +9511,10 @@
         <v>No</v>
       </c>
       <c r="M194" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N194" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O194" t="str">
         <v/>
@@ -9525,7 +9525,7 @@
         <v/>
       </c>
       <c r="B195" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C195" t="str">
         <v>Melemele Meadow</v>
@@ -9558,10 +9558,10 @@
         <v>No</v>
       </c>
       <c r="M195" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N195" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9572,7 +9572,7 @@
         <v/>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C196" t="str">
         <v>Melemele Meadow</v>
@@ -9605,10 +9605,10 @@
         <v>No</v>
       </c>
       <c r="M196" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N196" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9619,7 +9619,7 @@
         <v/>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Extra Challenge C-1</v>
       </c>
       <c r="C197" t="str">
         <v>Melemele Meadow</v>
@@ -9652,10 +9652,10 @@
         <v>No</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Ruins of Conflict</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"catchSpeciesUniqueCount":2}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="C199" t="str">
         <v>Kala'e Bay</v>
@@ -9746,10 +9746,10 @@
         <v>No</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Sacred Shrine</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kala'e Bay","count":15}}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Extra Challenge C-3</v>
       </c>
       <c r="B200" t="str">
-        <v/>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="C200" t="str">
         <v>Kala'e Bay</v>
@@ -9793,10 +9793,10 @@
         <v>No</v>
       </c>
       <c r="M200" t="str">
-        <v/>
+        <v>Sacred Shrine</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Kala'e Bay","count":15}}</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="C202" t="str">
         <v>Sacred Shrine</v>
@@ -9890,7 +9890,7 @@
         <v/>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tapu Koko","count":1},{"species":"Tapu Lele","count":1},{"species":"Tapu Bulu","count":1},{"species":"Tapu Fini","count":1}]}</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9898,10 +9898,10 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v/>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B203" t="str">
-        <v/>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="C203" t="str">
         <v>Sacred Shrine</v>
@@ -9937,7 +9937,7 @@
         <v/>
       </c>
       <c r="N203" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tapu Koko","count":1},{"species":"Tapu Lele","count":1},{"species":"Tapu Bulu","count":1},{"species":"Tapu Fini","count":1}]}</v>
       </c>
       <c r="O203" t="str">
         <v/>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Extra Challenge C-4</v>
       </c>
       <c r="B204" t="str">
-        <v/>
+        <v>Extra Challenge C-5</v>
       </c>
       <c r="C204" t="str">
         <v>Sacred Shrine</v>
@@ -9984,7 +9984,7 @@
         <v/>
       </c>
       <c r="N204" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tapu Koko","count":1},{"species":"Tapu Lele","count":1},{"species":"Tapu Bulu","count":1},{"species":"Tapu Fini","count":1}]}</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B206" t="str">
-        <v/>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="C206" t="str">
         <v>Poni Coast</v>
@@ -10075,10 +10075,10 @@
         <v>No</v>
       </c>
       <c r="M206" t="str">
-        <v/>
+        <v>Resolution Cave</v>
       </c>
       <c r="N206" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Normal","count":3}}</v>
       </c>
       <c r="O206" t="str">
         <v/>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Extra Challenge D-1</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>Extra Challenge D-2</v>
       </c>
       <c r="C207" t="str">
         <v>Poni Coast</v>
@@ -10122,10 +10122,10 @@
         <v>No</v>
       </c>
       <c r="M207" t="str">
-        <v/>
+        <v>Resolution Cave</v>
       </c>
       <c r="N207" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Normal","count":3}}</v>
       </c>
       <c r="O207" t="str">
         <v/>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C209" t="str">
         <v>The Interdimensional Rift</v>
@@ -10219,7 +10219,7 @@
         <v/>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C210" t="str">
         <v>The Interdimensional Rift</v>
@@ -10266,7 +10266,7 @@
         <v/>
       </c>
       <c r="N210" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O210" t="str">
         <v/>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C211" t="str">
         <v>The Interdimensional Rift</v>
@@ -10313,7 +10313,7 @@
         <v/>
       </c>
       <c r="N211" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O211" t="str">
         <v/>
@@ -10321,10 +10321,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B212" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C212" t="str">
         <v>The Interdimensional Rift</v>
@@ -10360,7 +10360,7 @@
         <v/>
       </c>
       <c r="N212" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O212" t="str">
         <v/>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B213" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C213" t="str">
         <v>The Interdimensional Rift</v>
@@ -10407,7 +10407,7 @@
         <v/>
       </c>
       <c r="N213" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O213" t="str">
         <v/>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B214" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C214" t="str">
         <v>The Interdimensional Rift</v>
@@ -10454,7 +10454,7 @@
         <v/>
       </c>
       <c r="N214" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O214" t="str">
         <v/>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B215" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C215" t="str">
         <v>The Interdimensional Rift</v>
@@ -10501,7 +10501,7 @@
         <v/>
       </c>
       <c r="N215" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O215" t="str">
         <v/>
@@ -10509,10 +10509,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C216" t="str">
         <v>The Interdimensional Rift</v>
@@ -10548,7 +10548,7 @@
         <v/>
       </c>
       <c r="N216" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O216" t="str">
         <v/>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v/>
+        <v>Extra Challenge D-4</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>Extra Challenge D-5</v>
       </c>
       <c r="C217" t="str">
         <v>The Interdimensional Rift</v>
@@ -10595,7 +10595,7 @@
         <v/>
       </c>
       <c r="N217" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"The Interdimensional Rift","count":100}}</v>
       </c>
       <c r="O217" t="str">
         <v/>
@@ -10627,7 +10627,7 @@
         <v>0.5</v>
       </c>
       <c r="I218" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J218" t="str">
         <v/>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v/>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B219" t="str">
-        <v/>
+        <v>Extra Challenge E-2</v>
       </c>
       <c r="C219" t="str">
         <v>Aether Paradise Labs</v>
@@ -10674,7 +10674,7 @@
         <v>0.5</v>
       </c>
       <c r="I219" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J219" t="str">
         <v/>
@@ -10686,10 +10686,10 @@
         <v>No</v>
       </c>
       <c r="M219" t="str">
-        <v/>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="N219" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O219" t="str">
         <v/>
@@ -10697,10 +10697,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v/>
+        <v>Extra Challenge E-1</v>
       </c>
       <c r="B220" t="str">
-        <v/>
+        <v>Extra Challenge E-2</v>
       </c>
       <c r="C220" t="str">
         <v>Aether Paradise Labs</v>
@@ -10721,7 +10721,7 @@
         <v>0.1</v>
       </c>
       <c r="I220" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J220" t="str">
         <v/>
@@ -10733,10 +10733,10 @@
         <v>No</v>
       </c>
       <c r="M220" t="str">
-        <v/>
+        <v>Aether Paradise Secret Lab</v>
       </c>
       <c r="N220" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Uncommon+","count":5}}</v>
       </c>
       <c r="O220" t="str">
         <v/>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Extra Challenge E-3</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="C223" t="str">
         <v>Lake of the Sunne</v>
@@ -10874,10 +10874,10 @@
         <v>No</v>
       </c>
       <c r="M223" t="str">
-        <v/>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="N223" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O223" t="str">
         <v/>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Extra Challenge E-3</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="C224" t="str">
         <v>Lake of the Sunne</v>
@@ -10921,10 +10921,10 @@
         <v>No</v>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>Obsidian Sphere</v>
       </c>
       <c r="N224" t="str">
-        <v/>
+        <v>{"catchByQuality":{"quality":"Epic+","count":1}}</v>
       </c>
       <c r="O224" t="str">
         <v/>
@@ -10979,7 +10979,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Extra Challenge E-4</v>
       </c>
       <c r="B226" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Extra Challenge E-5</v>
       </c>
       <c r="B228" t="str">
-        <v/>
+        <v>Extra Challenge E-6</v>
       </c>
       <c r="C228" t="str">
         <v>Obsidian Tesseract</v>
@@ -11112,7 +11112,7 @@
         <v/>
       </c>
       <c r="N228" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Necrozma","count":1},{"species":"Cosmog","count":1},{"species":"Cosmoem","count":1}]}</v>
       </c>
       <c r="O228" t="str">
         <v/>
@@ -11120,10 +11120,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Extra Challenge E-5</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>Extra Challenge E-6</v>
       </c>
       <c r="C229" t="str">
         <v>Obsidian Tesseract</v>
@@ -11159,7 +11159,7 @@
         <v/>
       </c>
       <c r="N229" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Necrozma","count":1},{"species":"Cosmog","count":1},{"species":"Cosmoem","count":1}]}</v>
       </c>
       <c r="O229" t="str">
         <v/>

--- a/7_Alola_Data.xlsx
+++ b/7_Alola_Data.xlsx
@@ -2819,7 +2819,7 @@
         <v>10-15</v>
       </c>
       <c r="G52" t="str">
-        <v>5-7</v>
+        <v>6-8</v>
       </c>
       <c r="H52" s="1">
         <v>0.25</v>
@@ -2866,7 +2866,7 @@
         <v>10-15</v>
       </c>
       <c r="G53" t="str">
-        <v>5-7</v>
+        <v>6-8</v>
       </c>
       <c r="H53" s="1">
         <v>0.25</v>
@@ -2913,7 +2913,7 @@
         <v>10-15</v>
       </c>
       <c r="G54" t="str">
-        <v>5-7</v>
+        <v>6-8</v>
       </c>
       <c r="H54" s="1">
         <v>0.25</v>
@@ -2960,7 +2960,7 @@
         <v>10-15</v>
       </c>
       <c r="G55" t="str">
-        <v>5-7</v>
+        <v>6-8</v>
       </c>
       <c r="H55" s="1">
         <v>0.25</v>
@@ -3007,7 +3007,7 @@
         <v>14-19</v>
       </c>
       <c r="G56" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H56" s="1">
         <v>0.2</v>
@@ -3054,7 +3054,7 @@
         <v>14-19</v>
       </c>
       <c r="G57" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H57" s="1">
         <v>0.2</v>
@@ -3101,7 +3101,7 @@
         <v>14-19</v>
       </c>
       <c r="G58" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H58" s="1">
         <v>0.2</v>
@@ -3148,7 +3148,7 @@
         <v>14-19</v>
       </c>
       <c r="G59" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H59" s="1">
         <v>0.2</v>
@@ -3195,7 +3195,7 @@
         <v>14-19</v>
       </c>
       <c r="G60" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H60" s="1">
         <v>0.2</v>
@@ -3242,7 +3242,7 @@
         <v>14-19</v>
       </c>
       <c r="G61" t="str">
-        <v>7-9</v>
+        <v>8-10</v>
       </c>
       <c r="H61" s="1">
         <v>0.1</v>
@@ -3336,7 +3336,7 @@
         <v>20-25</v>
       </c>
       <c r="G63" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H63" s="1">
         <v>0.25</v>
@@ -3383,7 +3383,7 @@
         <v>20-25</v>
       </c>
       <c r="G64" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H64" s="1">
         <v>0.25</v>
@@ -3430,7 +3430,7 @@
         <v>20-25</v>
       </c>
       <c r="G65" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H65" s="1">
         <v>0.25</v>
@@ -3477,7 +3477,7 @@
         <v>20-25</v>
       </c>
       <c r="G66" t="str">
-        <v>11-13</v>
+        <v>12-15</v>
       </c>
       <c r="H66" s="1">
         <v>0.25</v>
@@ -3571,7 +3571,7 @@
         <v>23-28</v>
       </c>
       <c r="G68" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H68" s="1">
         <v>0.3333</v>
@@ -3618,7 +3618,7 @@
         <v>23-28</v>
       </c>
       <c r="G69" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H69" s="1">
         <v>0.3333</v>
@@ -3665,7 +3665,7 @@
         <v>23-28</v>
       </c>
       <c r="G70" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H70" s="1">
         <v>0.3333</v>
@@ -3712,7 +3712,7 @@
         <v>23-28</v>
       </c>
       <c r="G71" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H71" s="1">
         <v>0.1</v>
@@ -3806,7 +3806,7 @@
         <v>28-33</v>
       </c>
       <c r="G73" t="str">
-        <v>19-22</v>
+        <v>20-23</v>
       </c>
       <c r="H73" s="1">
         <v>0.3333</v>
@@ -3853,7 +3853,7 @@
         <v>28-33</v>
       </c>
       <c r="G74" t="str">
-        <v>19-22</v>
+        <v>20-23</v>
       </c>
       <c r="H74" s="1">
         <v>0.3333</v>
@@ -3900,7 +3900,7 @@
         <v>28-33</v>
       </c>
       <c r="G75" t="str">
-        <v>19-22</v>
+        <v>20-23</v>
       </c>
       <c r="H75" s="1">
         <v>0.3333</v>
@@ -3994,7 +3994,7 @@
         <v>31-36</v>
       </c>
       <c r="G77" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H77" s="1">
         <v>0.2</v>
@@ -4041,7 +4041,7 @@
         <v>31-36</v>
       </c>
       <c r="G78" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H78" s="1">
         <v>0.2</v>
@@ -4088,7 +4088,7 @@
         <v>31-36</v>
       </c>
       <c r="G79" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H79" s="1">
         <v>0.2</v>
@@ -4135,7 +4135,7 @@
         <v>31-36</v>
       </c>
       <c r="G80" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H80" s="1">
         <v>0.2</v>
@@ -4182,7 +4182,7 @@
         <v>31-36</v>
       </c>
       <c r="G81" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H81" s="1">
         <v>0.2</v>
@@ -4229,7 +4229,7 @@
         <v>31-36</v>
       </c>
       <c r="G82" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H82" s="1">
         <v>0.1</v>
@@ -4276,7 +4276,7 @@
         <v>32-37</v>
       </c>
       <c r="G83" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H83" s="1">
         <v>0.2</v>
@@ -4323,7 +4323,7 @@
         <v>32-37</v>
       </c>
       <c r="G84" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H84" s="1">
         <v>0.2</v>
@@ -4370,7 +4370,7 @@
         <v>32-37</v>
       </c>
       <c r="G85" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H85" s="1">
         <v>0.2</v>
@@ -4417,7 +4417,7 @@
         <v>32-37</v>
       </c>
       <c r="G86" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H86" s="1">
         <v>0.2</v>
@@ -4464,7 +4464,7 @@
         <v>32-37</v>
       </c>
       <c r="G87" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H87" s="1">
         <v>0.2</v>
@@ -4511,7 +4511,7 @@
         <v>34-39</v>
       </c>
       <c r="G88" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H88" s="1">
         <v>0.16670000000000001</v>
@@ -4558,7 +4558,7 @@
         <v>34-39</v>
       </c>
       <c r="G89" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H89" s="1">
         <v>0.16670000000000001</v>
@@ -4605,7 +4605,7 @@
         <v>34-39</v>
       </c>
       <c r="G90" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H90" s="1">
         <v>0.16670000000000001</v>
@@ -4652,7 +4652,7 @@
         <v>34-39</v>
       </c>
       <c r="G91" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H91" s="1">
         <v>0.16670000000000001</v>
@@ -4699,7 +4699,7 @@
         <v>34-39</v>
       </c>
       <c r="G92" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H92" s="1">
         <v>0.16670000000000001</v>
@@ -4746,7 +4746,7 @@
         <v>34-39</v>
       </c>
       <c r="G93" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H93" s="1">
         <v>0.16670000000000001</v>
@@ -4793,7 +4793,7 @@
         <v>34-39</v>
       </c>
       <c r="G94" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H94" s="1">
         <v>0.1</v>
@@ -4840,7 +4840,7 @@
         <v>35-40</v>
       </c>
       <c r="G95" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H95" s="1">
         <v>0.2</v>
@@ -4887,7 +4887,7 @@
         <v>35-40</v>
       </c>
       <c r="G96" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H96" s="1">
         <v>0.2</v>
@@ -4934,7 +4934,7 @@
         <v>35-40</v>
       </c>
       <c r="G97" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H97" s="1">
         <v>0.2</v>
@@ -4981,7 +4981,7 @@
         <v>35-40</v>
       </c>
       <c r="G98" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H98" s="1">
         <v>0.2</v>
@@ -5028,7 +5028,7 @@
         <v>35-40</v>
       </c>
       <c r="G99" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H99" s="1">
         <v>0.2</v>
@@ -5075,7 +5075,7 @@
         <v>38-43</v>
       </c>
       <c r="G100" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H100" s="1">
         <v>0.25</v>
@@ -5122,7 +5122,7 @@
         <v>38-43</v>
       </c>
       <c r="G101" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H101" s="1">
         <v>0.25</v>
@@ -5169,7 +5169,7 @@
         <v>38-43</v>
       </c>
       <c r="G102" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H102" s="1">
         <v>0.25</v>
@@ -5216,7 +5216,7 @@
         <v>38-43</v>
       </c>
       <c r="G103" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H103" s="1">
         <v>0.25</v>
@@ -5263,7 +5263,7 @@
         <v>43-48</v>
       </c>
       <c r="G104" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H104" s="1">
         <v>0.125</v>
@@ -5310,7 +5310,7 @@
         <v>43-48</v>
       </c>
       <c r="G105" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H105" s="1">
         <v>0.125</v>
@@ -5357,7 +5357,7 @@
         <v>43-48</v>
       </c>
       <c r="G106" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H106" s="1">
         <v>0.125</v>
@@ -5404,7 +5404,7 @@
         <v>43-48</v>
       </c>
       <c r="G107" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H107" s="1">
         <v>0.125</v>
@@ -5451,7 +5451,7 @@
         <v>43-48</v>
       </c>
       <c r="G108" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H108" s="1">
         <v>0.125</v>
@@ -5498,7 +5498,7 @@
         <v>43-48</v>
       </c>
       <c r="G109" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H109" s="1">
         <v>0.125</v>
@@ -5545,7 +5545,7 @@
         <v>43-48</v>
       </c>
       <c r="G110" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H110" s="1">
         <v>0.125</v>
@@ -5592,7 +5592,7 @@
         <v>43-48</v>
       </c>
       <c r="G111" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H111" s="1">
         <v>0.125</v>
@@ -5639,7 +5639,7 @@
         <v>48-53</v>
       </c>
       <c r="G112" t="str">
-        <v>35-38</v>
+        <v>38-41</v>
       </c>
       <c r="H112" s="1">
         <v>0.2</v>
@@ -5686,7 +5686,7 @@
         <v>48-53</v>
       </c>
       <c r="G113" t="str">
-        <v>35-38</v>
+        <v>38-41</v>
       </c>
       <c r="H113" s="1">
         <v>0.2</v>
@@ -5733,7 +5733,7 @@
         <v>48-53</v>
       </c>
       <c r="G114" t="str">
-        <v>35-38</v>
+        <v>38-41</v>
       </c>
       <c r="H114" s="1">
         <v>0.2</v>
@@ -5780,7 +5780,7 @@
         <v>48-53</v>
       </c>
       <c r="G115" t="str">
-        <v>35-38</v>
+        <v>38-41</v>
       </c>
       <c r="H115" s="1">
         <v>0.2</v>
@@ -5827,7 +5827,7 @@
         <v>48-53</v>
       </c>
       <c r="G116" t="str">
-        <v>35-38</v>
+        <v>38-41</v>
       </c>
       <c r="H116" s="1">
         <v>0.2</v>
@@ -5874,7 +5874,7 @@
         <v>52-57</v>
       </c>
       <c r="G117" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H117" s="1">
         <v>0.25</v>
@@ -5921,7 +5921,7 @@
         <v>52-57</v>
       </c>
       <c r="G118" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H118" s="1">
         <v>0.25</v>
@@ -5968,7 +5968,7 @@
         <v>52-57</v>
       </c>
       <c r="G119" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H119" s="1">
         <v>0.25</v>
@@ -6015,7 +6015,7 @@
         <v>52-57</v>
       </c>
       <c r="G120" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H120" s="1">
         <v>0.25</v>
@@ -6062,7 +6062,7 @@
         <v>58-63</v>
       </c>
       <c r="G121" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H121" s="1">
         <v>0.2</v>
@@ -6109,7 +6109,7 @@
         <v>58-63</v>
       </c>
       <c r="G122" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H122" s="1">
         <v>0.2</v>
@@ -6156,7 +6156,7 @@
         <v>58-63</v>
       </c>
       <c r="G123" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H123" s="1">
         <v>0.2</v>
@@ -6203,7 +6203,7 @@
         <v>58-63</v>
       </c>
       <c r="G124" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H124" s="1">
         <v>0.2</v>
@@ -6250,7 +6250,7 @@
         <v>58-63</v>
       </c>
       <c r="G125" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H125" s="1">
         <v>0.2</v>
@@ -6297,7 +6297,7 @@
         <v>60-65</v>
       </c>
       <c r="G126" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H126" s="1">
         <v>0.16670000000000001</v>
@@ -6344,7 +6344,7 @@
         <v>60-65</v>
       </c>
       <c r="G127" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H127" s="1">
         <v>0.16670000000000001</v>
@@ -6391,7 +6391,7 @@
         <v>60-65</v>
       </c>
       <c r="G128" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H128" s="1">
         <v>0.16670000000000001</v>
@@ -6438,7 +6438,7 @@
         <v>60-65</v>
       </c>
       <c r="G129" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H129" s="1">
         <v>0.16670000000000001</v>
@@ -6485,7 +6485,7 @@
         <v>60-65</v>
       </c>
       <c r="G130" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H130" s="1">
         <v>0.16670000000000001</v>
@@ -6532,7 +6532,7 @@
         <v>60-65</v>
       </c>
       <c r="G131" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H131" s="1">
         <v>0.16670000000000001</v>
@@ -6579,7 +6579,7 @@
         <v>63-68</v>
       </c>
       <c r="G132" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H132" s="1">
         <v>0.25</v>
@@ -6626,7 +6626,7 @@
         <v>63-68</v>
       </c>
       <c r="G133" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H133" s="1">
         <v>0.25</v>
@@ -6673,7 +6673,7 @@
         <v>63-68</v>
       </c>
       <c r="G134" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H134" s="1">
         <v>0.25</v>
@@ -6720,7 +6720,7 @@
         <v>63-68</v>
       </c>
       <c r="G135" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H135" s="1">
         <v>0.25</v>
@@ -6767,7 +6767,7 @@
         <v>63-68</v>
       </c>
       <c r="G136" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H136" s="1">
         <v>0.1</v>
@@ -6861,7 +6861,7 @@
         <v>70-75</v>
       </c>
       <c r="G138" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H138" s="1">
         <v>0.2</v>
@@ -6908,7 +6908,7 @@
         <v>70-75</v>
       </c>
       <c r="G139" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H139" s="1">
         <v>0.2</v>
@@ -6955,7 +6955,7 @@
         <v>70-75</v>
       </c>
       <c r="G140" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H140" s="1">
         <v>0.2</v>
@@ -7002,7 +7002,7 @@
         <v>70-75</v>
       </c>
       <c r="G141" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H141" s="1">
         <v>0.2</v>
@@ -7049,7 +7049,7 @@
         <v>70-75</v>
       </c>
       <c r="G142" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H142" s="1">
         <v>0.2</v>
@@ -7096,7 +7096,7 @@
         <v>72-77</v>
       </c>
       <c r="G143" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="H143" s="1">
         <v>0.2</v>
@@ -7143,7 +7143,7 @@
         <v>72-77</v>
       </c>
       <c r="G144" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="H144" s="1">
         <v>0.2</v>
@@ -7190,7 +7190,7 @@
         <v>72-77</v>
       </c>
       <c r="G145" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="H145" s="1">
         <v>0.2</v>
@@ -7237,7 +7237,7 @@
         <v>72-77</v>
       </c>
       <c r="G146" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="H146" s="1">
         <v>0.2</v>
@@ -7284,7 +7284,7 @@
         <v>72-77</v>
       </c>
       <c r="G147" t="str">
-        <v>50-55</v>
+        <v>53-58</v>
       </c>
       <c r="H147" s="1">
         <v>0.2</v>
@@ -7331,7 +7331,7 @@
         <v>73-78</v>
       </c>
       <c r="G148" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H148" s="1">
         <v>0.16670000000000001</v>
@@ -7378,7 +7378,7 @@
         <v>73-78</v>
       </c>
       <c r="G149" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H149" s="1">
         <v>0.16670000000000001</v>
@@ -7425,7 +7425,7 @@
         <v>73-78</v>
       </c>
       <c r="G150" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H150" s="1">
         <v>0.16670000000000001</v>
@@ -7472,7 +7472,7 @@
         <v>73-78</v>
       </c>
       <c r="G151" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H151" s="1">
         <v>0.16670000000000001</v>
@@ -7519,7 +7519,7 @@
         <v>73-78</v>
       </c>
       <c r="G152" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H152" s="1">
         <v>0.16670000000000001</v>
@@ -7566,7 +7566,7 @@
         <v>73-78</v>
       </c>
       <c r="G153" t="str">
-        <v>52-57</v>
+        <v>55-60</v>
       </c>
       <c r="H153" s="1">
         <v>0.16670000000000001</v>
@@ -7613,7 +7613,7 @@
         <v>75-80</v>
       </c>
       <c r="G154" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="H154" s="1">
         <v>0.3333</v>
@@ -7660,7 +7660,7 @@
         <v>75-80</v>
       </c>
       <c r="G155" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="H155" s="1">
         <v>0.3333</v>
@@ -7707,7 +7707,7 @@
         <v>75-80</v>
       </c>
       <c r="G156" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="H156" s="1">
         <v>0.3333</v>
@@ -7754,7 +7754,7 @@
         <v>75-80</v>
       </c>
       <c r="G157" t="str">
-        <v>54-59</v>
+        <v>57-62</v>
       </c>
       <c r="H157" s="1">
         <v>0.1</v>
@@ -7895,7 +7895,7 @@
         <v>82-87</v>
       </c>
       <c r="G160" t="str">
-        <v>60-66</v>
+        <v>63-69</v>
       </c>
       <c r="H160" s="1">
         <v>0.25</v>
@@ -7942,7 +7942,7 @@
         <v>82-87</v>
       </c>
       <c r="G161" t="str">
-        <v>60-66</v>
+        <v>63-69</v>
       </c>
       <c r="H161" s="1">
         <v>0.25</v>
@@ -7989,7 +7989,7 @@
         <v>82-87</v>
       </c>
       <c r="G162" t="str">
-        <v>60-66</v>
+        <v>63-69</v>
       </c>
       <c r="H162" s="1">
         <v>0.25</v>
@@ -8036,7 +8036,7 @@
         <v>82-87</v>
       </c>
       <c r="G163" t="str">
-        <v>60-66</v>
+        <v>63-69</v>
       </c>
       <c r="H163" s="1">
         <v>0.25</v>
@@ -8318,7 +8318,7 @@
         <v>85-90</v>
       </c>
       <c r="G169" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H169" s="1">
         <v>0.25</v>
@@ -8365,7 +8365,7 @@
         <v>85-90</v>
       </c>
       <c r="G170" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H170" s="1">
         <v>0.25</v>
@@ -8412,7 +8412,7 @@
         <v>85-90</v>
       </c>
       <c r="G171" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H171" s="1">
         <v>0.25</v>
@@ -8459,7 +8459,7 @@
         <v>85-90</v>
       </c>
       <c r="G172" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H172" s="1">
         <v>0.25</v>
@@ -9728,7 +9728,7 @@
         <v>100-100</v>
       </c>
       <c r="G199" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H199" s="1">
         <v>0.25</v>
@@ -9775,7 +9775,7 @@
         <v>100-100</v>
       </c>
       <c r="G200" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H200" s="1">
         <v>0.25</v>
@@ -9822,7 +9822,7 @@
         <v>100-100</v>
       </c>
       <c r="G201" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H201" s="1">
         <v>0.25</v>
@@ -9869,7 +9869,7 @@
         <v>100-100</v>
       </c>
       <c r="G202" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H202" s="1">
         <v>0.25</v>
